--- a/ROUTE_3_PATH3_MBA_ADMIN_ECE_LIB_AUDI/PATH3_FINAL_ODK.xlsx
+++ b/ROUTE_3_PATH3_MBA_ADMIN_ECE_LIB_AUDI/PATH3_FINAL_ODK.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I67"/>
+  <dimension ref="A1:J76"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -418,15 +418,18 @@
         <v>required</v>
       </c>
       <c r="F1" t="str">
+        <v>required_message</v>
+      </c>
+      <c r="G1" t="str">
         <v>constraint</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>constraint_message</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>relevant</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>media::image</v>
       </c>
     </row>
@@ -438,7 +441,7 @@
         <v>start_group</v>
       </c>
       <c r="C2" t="str">
-        <v>START — TEAM INFORMATION</v>
+        <v>START — REGISTRATION</v>
       </c>
     </row>
     <row r="3" xml:space="preserve">
@@ -446,22 +449,47 @@
         <v>note</v>
       </c>
       <c r="B3" t="str">
-        <v>start_rules_note</v>
+        <v>instructions_rules_note</v>
       </c>
       <c r="C3" t="str" xml:space="preserve">
         <v xml:space="preserve">🏆 FINAL CLUE — PATH 3
-### 🏴 TREASURE HUNT — RULES
-1. *No phones allowed* during the hunt. Keep them switched off and safely stored.
-2. *Stay with your team* and follow the designated route/instructions.
-3. *No cheating or interference* with other teams, clues, props, or college property.
-4. Complete all challenges *as instructed by the coordinators*. Safety comes first.
-5. Any violation of the rules may result in a *time penalty or disqualification*. The coordinator’s decision will be final.
-⚠️ IMPORTANT:
-• All questions, code entries, and photo uploads are MANDATORY.
-• All text answers and codes must be entered in UPPERCASE ONLY.</v>
+TREASURE HUNT FOR FRESHERS 2026
+Welcome to PATH 3 of the Final Clue Treasure Hunt!
+Instructions:
+Rules and Regulations:
+* Participants must report to the designated starting point 5–10 minutes before the event begins.
+* Each team must consist of 3–4 members.
+* At least one member of the team should have an Android phone.
+* Each team will receive the first clue at the beginning of the event.
+* Teams must solve each clue to find the location of the next clue.
+* Clues must be solved in the given sequence.
+* Teams are not allowed to take, hide, damage, or tamper with clues belonging to other teams.
+* Teams must remain within the designated event area.
+* Running in unsafe areas or restricted zones is prohibited.
+* Participants must not enter restricted areas or disturb ongoing events/classes.
+* Physical force, pushing, blocking, or interfering with other teams is strictly prohibited.
+* Only one device containing ODK Collect is allowed per team.
+* No use of Wi-Fi unless specifically specified. Otherwise, the team may be disqualified.
+* Participants must not damage or move any property while searching for clues.
+* Teams must follow instructions given by volunteers and organizers at all times.
+* Asking people outside the team for answers or assistance is not allowed.
+* Teams must not follow, copy, or deliberately interfere with another team's progress.
+* Tampering with clues, cheating, entering restricted areas, or intentionally misleading other teams may result in immediate disqualification.
+* The Organizing Committee will not be responsible for the loss or damage of any personal belongings of participants.
+🏆 TEAM QUALIFICATION RULES (PER PATH):
+There are 5 rounds in each path.
+From each path:
+* First 25 teams proceed to Round 2.
+* Next 15 teams proceed to Round 3.
+* Next 7 teams proceed to Round 4.
+* Next 2 teams proceed to Round 5.
+⚠️ MANDATORY RESPONSE &amp; CAPS ONLY RULES:
+• Every single question, photo upload, and code entry is strictly MANDATORY.
+• All text answers and volunteer codes must be entered in UPPERCASE (CAPS ONLY).
+• Lowercase letters will be rejected by validation.</v>
       </c>
       <c r="D3" t="str">
-        <v>Read all rules carefully before proceeding.</v>
+        <v>Read all rules and instructions carefully.</v>
       </c>
     </row>
     <row r="4" xml:space="preserve">
@@ -472,7 +500,7 @@
         <v>team_name</v>
       </c>
       <c r="C4" t="str" xml:space="preserve">
-        <v xml:space="preserve">Enter Team Name
+        <v xml:space="preserve">Enter Team Name (MANDATORY)
 Enter code in caps</v>
       </c>
       <c r="D4" t="str">
@@ -482,9 +510,12 @@
         <v>yes</v>
       </c>
       <c r="F4" t="str">
+        <v>❌ Team Name is mandatory. Please enter in UPPERCASE.</v>
+      </c>
+      <c r="G4" t="str">
         <v>regex(., '^[A-Z0-9\-_ ]+$')</v>
       </c>
-      <c r="G4" t="str">
+      <c r="H4" t="str">
         <v>❌ Please enter Team Name in UPPERCASE (CAPS ONLY).</v>
       </c>
     </row>
@@ -493,10 +524,10 @@
         <v>text</v>
       </c>
       <c r="B5" t="str">
-        <v>team_id</v>
+        <v>player_id</v>
       </c>
       <c r="C5" t="str" xml:space="preserve">
-        <v xml:space="preserve">Enter Team ID
+        <v xml:space="preserve">Enter Team / Player Identification (MANDATORY)
 Enter code in caps</v>
       </c>
       <c r="D5" t="str">
@@ -506,10 +537,13 @@
         <v>yes</v>
       </c>
       <c r="F5" t="str">
+        <v>❌ Player / Team ID is mandatory. Please enter in UPPERCASE.</v>
+      </c>
+      <c r="G5" t="str">
         <v>regex(., '^[A-Z0-9\-_ ]+$')</v>
       </c>
-      <c r="G5" t="str">
-        <v>❌ Please enter Team ID in UPPERCASE (CAPS ONLY).</v>
+      <c r="H5" t="str">
+        <v>❌ Please enter Player/Team Identification in UPPERCASE (CAPS ONLY).</v>
       </c>
     </row>
     <row r="6" xml:space="preserve">
@@ -520,7 +554,7 @@
         <v>team_start_photo</v>
       </c>
       <c r="C6" t="str" xml:space="preserve">
-        <v xml:space="preserve">📸 Upload Team Verification Photo
+        <v xml:space="preserve">📸 Upload Team Verification Photo (MANDATORY)
 Photo upload is mandatory</v>
       </c>
       <c r="D6" t="str">
@@ -528,6 +562,9 @@
       </c>
       <c r="E6" t="str">
         <v>yes</v>
+      </c>
+      <c r="F6" t="str">
+        <v>❌ Team verification photo is strictly mandatory.</v>
       </c>
     </row>
     <row r="7">
@@ -545,8 +582,8 @@
       <c r="C8" t="str">
         <v>ROUND 1 — OBJECT FINDING</v>
       </c>
-      <c r="H8" t="str">
-        <v>${team_name} != '' and ${team_id} != '' and ${team_start_photo} != ''</v>
+      <c r="I8" t="str">
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != ''</v>
       </c>
     </row>
     <row r="9" xml:space="preserve">
@@ -558,15 +595,15 @@
       </c>
       <c r="C9" t="str" xml:space="preserve">
         <v xml:space="preserve">📍 ROUND 1: 🧩 OBJECT FINDING
-Challenge: Locate the assigned hidden object/code at this station.
 Instructions:
-1. Search the location to find the assigned hidden object.
-2. Take a clear photo of the object.
-3. Show the photo to the station volunteer to receive your verification code.
+1. Search the location to find the designated Visvesvaraya-related physical object.
+2. Take a mandatory photo of the object.
+3. Show the object/photo to the nearby Luminus volunteer.
+4. Enter the verification code given by the volunteer.
 Enter code in caps</v>
       </c>
       <c r="D9" t="str">
-        <v>Find the assigned hidden object.</v>
+        <v>Find the Visvesvaraya object, take photo, and ask volunteer for code.</v>
       </c>
     </row>
     <row r="10" xml:space="preserve">
@@ -577,14 +614,17 @@
         <v>r1_mba_photo</v>
       </c>
       <c r="C10" t="str" xml:space="preserve">
-        <v xml:space="preserve">📸 Upload Photo of Discovered Hidden Object
+        <v xml:space="preserve">📸 Upload Photo of Discovered Hidden Object (MANDATORY)
 Photo upload is mandatory</v>
       </c>
       <c r="D10" t="str">
-        <v>Take a clear photo of the discovered object.</v>
+        <v>Take a clear photo of the discovered Visvesvaraya object.</v>
       </c>
       <c r="E10" t="str">
         <v>yes</v>
+      </c>
+      <c r="F10" t="str">
+        <v>❌ Photo upload of the object is strictly mandatory.</v>
       </c>
     </row>
     <row r="11" xml:space="preserve">
@@ -595,7 +635,7 @@
         <v>r1_mba_code</v>
       </c>
       <c r="C11" t="str" xml:space="preserve">
-        <v xml:space="preserve">Enter Volunteer Verification Code
+        <v xml:space="preserve">Enter Volunteer Verification Code (MANDATORY)
 Enter code in caps</v>
       </c>
       <c r="D11" t="str">
@@ -605,10 +645,13 @@
         <v>yes</v>
       </c>
       <c r="F11" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ENG-KID-119'</v>
+        <v>❌ Volunteer verification code is mandatory.</v>
       </c>
       <c r="G11" t="str">
-        <v>❌ Incorrect code. Enter ENG-KID-119 in CAPS provided by the volunteer.</v>
+        <v>regex(., '^[A-Z0-9\-_]+$') and normalize-space(.) = 'ENG-KID-119'</v>
+      </c>
+      <c r="H11" t="str">
+        <v>❌ Incorrect code. Check the object again and enter the code exactly as displayed.</v>
       </c>
     </row>
     <row r="12">
@@ -626,8 +669,8 @@
       <c r="C13" t="str">
         <v>ROUND 2 LOCATION CLUE</v>
       </c>
-      <c r="H13" t="str">
-        <v>${team_name} != '' and ${team_id} != '' and ${team_start_photo} != '' and translate(normalize-space(${r1_mba_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ENG-KID-119' and ${r1_mba_photo} != ''</v>
+      <c r="I13" t="str">
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_mba_code}) = 'ENG-KID-119' and ${r1_mba_photo} != ''</v>
       </c>
     </row>
     <row r="14" xml:space="preserve">
@@ -639,14 +682,14 @@
       </c>
       <c r="C14" t="str" xml:space="preserve">
         <v xml:space="preserve">📍 ROUND 2 LOCATION CLUE: ELEMENTAL ENCRYPTION
-Examine the periodic table elements in the puzzle image below.
-Decode the chemical symbols by taking the first letter of each element to reveal your next block destination!
+Decode the chemical symbols using the periodic table. Take the first letter of each identified element and atomic numbers to reveal your next location.
+Examine the image attached below carefully.
 Enter code in caps</v>
       </c>
       <c r="D14" t="str">
-        <v>Decode the chemical symbols in the image to find the destination.</v>
-      </c>
-      <c r="I14" t="str">
+        <v>Decode the chemical symbols in the image to discover your next location.</v>
+      </c>
+      <c r="J14" t="str">
         <v>challenge.jpeg</v>
       </c>
     </row>
@@ -658,7 +701,7 @@
         <v>r2_admin_block_answer</v>
       </c>
       <c r="C15" t="str" xml:space="preserve">
-        <v xml:space="preserve">Which campus block does this elemental encryption direct your team to?
+        <v xml:space="preserve">Enter your decoded destination location: (MANDATORY)
 Enter code in caps</v>
       </c>
       <c r="D15" t="str">
@@ -668,77 +711,104 @@
         <v>yes</v>
       </c>
       <c r="F15" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ADMIN' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ADMIN BLOCK'</v>
+        <v>❌ Destination location is mandatory.</v>
       </c>
       <c r="G15" t="str">
-        <v>❌ Incorrect destination. Decode the chemical symbols to identify the block in CAPS.</v>
-      </c>
-      <c r="I15" t="str">
+        <v>regex(., '^[A-Z ]+$') and (normalize-space(.) = 'ADMIN' or normalize-space(.) = 'ADMIN BLOCK')</v>
+      </c>
+      <c r="H15" t="str">
+        <v>❌ That answer is not correct. Recheck the chemical symbols and try again.</v>
+      </c>
+      <c r="J15" t="str">
         <v>challenge.jpeg</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" xml:space="preserve">
       <c r="A16" t="str">
+        <v>note</v>
+      </c>
+      <c r="B16" t="str">
+        <v>r2_admin_proceed_note</v>
+      </c>
+      <c r="C16" t="str" xml:space="preserve">
+        <v xml:space="preserve">🏃 Correct! Proceed to your next location and enter the START CODE provided there.
+Enter code in caps</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Proceed to the location and ask volunteer for start code.</v>
+      </c>
+      <c r="I16" t="str">
+        <v>normalize-space(${r2_admin_block_answer}) = 'ADMIN' or normalize-space(${r2_admin_block_answer}) = 'ADMIN BLOCK'</v>
+      </c>
+    </row>
+    <row r="17" xml:space="preserve">
+      <c r="A17" t="str">
+        <v>text</v>
+      </c>
+      <c r="B17" t="str">
+        <v>r2_admin_start_code</v>
+      </c>
+      <c r="C17" t="str" xml:space="preserve">
+        <v xml:space="preserve">Enter START CODE from Volunteer (MANDATORY)
+Enter code in caps</v>
+      </c>
+      <c r="D17" t="str">
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+      </c>
+      <c r="E17" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F17" t="str">
+        <v>❌ START CODE is mandatory.</v>
+      </c>
+      <c r="G17" t="str">
+        <v>regex(., '^[A-Z0-9\-_]+$') and normalize-space(.) = 'ADMIN-START'</v>
+      </c>
+      <c r="H17" t="str">
+        <v>❌ Incorrect START CODE. Check with the location setup and enter the code exactly as provided.</v>
+      </c>
+      <c r="I17" t="str">
+        <v>normalize-space(${r2_admin_block_answer}) = 'ADMIN' or normalize-space(${r2_admin_block_answer}) = 'ADMIN BLOCK'</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
         <v>end_group</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="str">
+    <row r="19">
+      <c r="A19" t="str">
         <v>begin_group</v>
       </c>
-      <c r="B17" t="str">
-        <v>admin_start_group</v>
-      </c>
-      <c r="C17" t="str">
-        <v>ADMIN ARRIVAL</v>
-      </c>
-      <c r="H17" t="str">
-        <v>${team_name} != '' and ${team_id} != '' and ${team_start_photo} != '' and translate(normalize-space(${r1_mba_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ENG-KID-119' and ${r1_mba_photo} != '' and (translate(normalize-space(${r2_admin_block_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ADMIN' or translate(normalize-space(${r2_admin_block_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ADMIN BLOCK')</v>
-      </c>
-    </row>
-    <row r="18" xml:space="preserve">
-      <c r="A18" t="str">
-        <v>note</v>
-      </c>
-      <c r="B18" t="str">
-        <v>admin_arrival_note</v>
-      </c>
-      <c r="C18" t="str" xml:space="preserve">
-        <v xml:space="preserve">🏃 PROCEED TO ADMIN BLOCK
-Report immediately to the ADMIN station and meet the volunteer to receive your ADMIN start code.
-Enter code in caps</v>
-      </c>
-      <c r="D18" t="str">
-        <v>Meet volunteer at ADMIN station.</v>
-      </c>
-    </row>
-    <row r="19" xml:space="preserve">
-      <c r="A19" t="str">
-        <v>text</v>
-      </c>
       <c r="B19" t="str">
-        <v>r2_admin_start_code</v>
-      </c>
-      <c r="C19" t="str" xml:space="preserve">
-        <v xml:space="preserve">Enter ADMIN Start Code
-Enter code in caps</v>
-      </c>
-      <c r="D19" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
-      </c>
-      <c r="E19" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F19" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ADMIN-START'</v>
-      </c>
-      <c r="G19" t="str">
-        <v>❌ Incorrect start code. Enter ADMIN-START in CAPS provided by the volunteer.</v>
-      </c>
-    </row>
-    <row r="20">
+        <v>admin_mini_group</v>
+      </c>
+      <c r="C19" t="str">
+        <v>ROUND 2 — MINI CHALLENGE</v>
+      </c>
+      <c r="I19" t="str">
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_mba_code}) = 'ENG-KID-119' and ${r1_mba_photo} != '' and (normalize-space(${r2_admin_block_answer}) = 'ADMIN' or normalize-space(${r2_admin_block_answer}) = 'ADMIN BLOCK') and normalize-space(${r2_admin_start_code}) = 'ADMIN-START'</v>
+      </c>
+    </row>
+    <row r="20" xml:space="preserve">
       <c r="A20" t="str">
-        <v>end_group</v>
+        <v>select_one admin_variant_list</v>
+      </c>
+      <c r="B20" t="str">
+        <v>r2_admin_variant</v>
+      </c>
+      <c r="C20" t="str" xml:space="preserve">
+        <v xml:space="preserve">Select your assigned challenge variant: (MANDATORY)
+Mandatory selection</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Choose the variant assigned by the station volunteer.</v>
+      </c>
+      <c r="E20" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F20" t="str">
+        <v>❌ Selecting your assigned variant is mandatory.</v>
       </c>
     </row>
     <row r="21">
@@ -746,516 +816,679 @@
         <v>begin_group</v>
       </c>
       <c r="B21" t="str">
-        <v>admin_mini_group</v>
+        <v>admin_v1_group</v>
       </c>
       <c r="C21" t="str">
-        <v>ROUND 2 — MINI CHALLENGE</v>
-      </c>
-      <c r="H21" t="str">
-        <v>${team_name} != '' and ${team_id} != '' and ${team_start_photo} != '' and translate(normalize-space(${r1_mba_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ENG-KID-119' and ${r1_mba_photo} != '' and (translate(normalize-space(${r2_admin_block_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ADMIN' or translate(normalize-space(${r2_admin_block_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ADMIN BLOCK') and translate(normalize-space(${r2_admin_start_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ADMIN-START'</v>
+        <v>VARIANT A — COUNT TO UNLOCK</v>
+      </c>
+      <c r="I21" t="str">
+        <v>${r2_admin_variant} = 'var1'</v>
       </c>
     </row>
     <row r="22" xml:space="preserve">
       <c r="A22" t="str">
-        <v>select_one admin_variant_list</v>
+        <v>note</v>
       </c>
       <c r="B22" t="str">
-        <v>r2_admin_variant</v>
+        <v>admin_v1_intro</v>
       </c>
       <c r="C22" t="str" xml:space="preserve">
-        <v xml:space="preserve">Select Assigned Challenge Variant
-Mandatory selection</v>
+        <v xml:space="preserve">🔢 MINI-CHALLENGE: COUNT TO UNLOCK
+Look carefully around the decorated hall and count the specified objects. You may divide the search among your team members, but do not touch, move, or pick up anything.
+Enter code in caps</v>
       </c>
       <c r="D22" t="str">
-        <v>Choose the variant assigned by the station volunteer.</v>
-      </c>
-      <c r="E22" t="str">
-        <v>yes</v>
+        <v>Count all hidden objects accurately.</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>begin_group</v>
+        <v>integer</v>
       </c>
       <c r="B23" t="str">
-        <v>admin_v1_group</v>
+        <v>r2_v1_q1_chess</v>
       </c>
       <c r="C23" t="str">
-        <v>VARIANT 1 — COUNT TO UNLOCK</v>
+        <v>1. ♟️ How many chess pieces were hidden? (MANDATORY)</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Enter the exact integer count.</v>
+      </c>
+      <c r="E23" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F23" t="str">
+        <v>❌ Question 1 count is mandatory.</v>
+      </c>
+      <c r="G23" t="str">
+        <v>. = 5</v>
       </c>
       <c r="H23" t="str">
-        <v>${r2_admin_variant} = 'var1'</v>
-      </c>
-    </row>
-    <row r="24" xml:space="preserve">
+        <v>❌ Incorrect count for chess pieces.</v>
+      </c>
+    </row>
+    <row r="24">
       <c r="A24" t="str">
-        <v>note</v>
+        <v>integer</v>
       </c>
       <c r="B24" t="str">
-        <v>admin_v1_intro</v>
-      </c>
-      <c r="C24" t="str" xml:space="preserve">
-        <v xml:space="preserve">🔢 MINI-CHALLENGE: COUNT TO UNLOCK
-Teams have 3–4 minutes to find and count the hidden objects in the decorated seminar hall without touching anything.
-Objects to find:
-• Caps
-• Chess pieces
-• UNO cards
-• Sunglasses
-• Keys/Keychains
-• Water bottles
-Rules: Do not touch or move any objects. Submit counts to volunteer to clear at least 4 out of 6.
-Enter code in caps</v>
+        <v>r2_v1_q2_uno</v>
+      </c>
+      <c r="C24" t="str">
+        <v>2. 🎴 How many UNO cards were hidden? (MANDATORY)</v>
       </c>
       <c r="D24" t="str">
-        <v>Count objects and submit to volunteer.</v>
-      </c>
-    </row>
-    <row r="25" xml:space="preserve">
+        <v>Enter the exact integer count.</v>
+      </c>
+      <c r="E24" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F24" t="str">
+        <v>❌ Question 2 count is mandatory.</v>
+      </c>
+      <c r="G24" t="str">
+        <v>. = 7</v>
+      </c>
+      <c r="H24" t="str">
+        <v>❌ Incorrect count for UNO cards.</v>
+      </c>
+    </row>
+    <row r="25">
       <c r="A25" t="str">
-        <v>image</v>
+        <v>integer</v>
       </c>
       <c r="B25" t="str">
-        <v>r2_v1_admin_photo</v>
-      </c>
-      <c r="C25" t="str" xml:space="preserve">
-        <v xml:space="preserve">📸 Upload Photo of Count to Unlock Station
-Photo upload is mandatory</v>
+        <v>r2_v1_q3_appy</v>
+      </c>
+      <c r="C25" t="str">
+        <v>3. 🧃 How many Appy juice bottles/packs were hidden? (MANDATORY)</v>
       </c>
       <c r="D25" t="str">
-        <v>Take a clear photo of your team at the station.</v>
+        <v>Enter the exact integer count.</v>
       </c>
       <c r="E25" t="str">
         <v>yes</v>
       </c>
-    </row>
-    <row r="26" xml:space="preserve">
+      <c r="F25" t="str">
+        <v>❌ Question 3 count is mandatory.</v>
+      </c>
+      <c r="G25" t="str">
+        <v>. = 3</v>
+      </c>
+      <c r="H25" t="str">
+        <v>❌ Incorrect count for Appy juice.</v>
+      </c>
+    </row>
+    <row r="26">
       <c r="A26" t="str">
-        <v>text</v>
+        <v>integer</v>
       </c>
       <c r="B26" t="str">
-        <v>r2_v1_code</v>
-      </c>
-      <c r="C26" t="str" xml:space="preserve">
-        <v xml:space="preserve">Enter Volunteer Clearance Code
-Enter code in caps</v>
+        <v>r2_v1_q4_smoodh</v>
+      </c>
+      <c r="C26" t="str">
+        <v>4. 🥛 How many Smoodh bottles were hidden? (MANDATORY)</v>
       </c>
       <c r="D26" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>Enter the exact integer count.</v>
       </c>
       <c r="E26" t="str">
         <v>yes</v>
       </c>
       <c r="F26" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ADM-DUCK-3'</v>
+        <v>❌ Question 4 count is mandatory.</v>
       </c>
       <c r="G26" t="str">
-        <v>❌ Incorrect code. Enter ADM-DUCK-3 in CAPS provided by the volunteer.</v>
+        <v>. = 4</v>
+      </c>
+      <c r="H26" t="str">
+        <v>❌ Incorrect count for Smoodh bottles.</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>end_group</v>
-      </c>
-    </row>
-    <row r="28">
+        <v>integer</v>
+      </c>
+      <c r="B27" t="str">
+        <v>r2_v1_q5_files</v>
+      </c>
+      <c r="C27" t="str">
+        <v>5. 📁 How many files were hidden? (MANDATORY)</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Enter the exact integer count.</v>
+      </c>
+      <c r="E27" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F27" t="str">
+        <v>❌ Question 5 count is mandatory.</v>
+      </c>
+      <c r="G27" t="str">
+        <v>. = 2</v>
+      </c>
+      <c r="H27" t="str">
+        <v>❌ Incorrect count for files.</v>
+      </c>
+    </row>
+    <row r="28" xml:space="preserve">
       <c r="A28" t="str">
-        <v>begin_group</v>
+        <v>image</v>
       </c>
       <c r="B28" t="str">
-        <v>admin_v2_group</v>
-      </c>
-      <c r="C28" t="str">
-        <v>VARIANT 2 — MEMORY ROOM</v>
-      </c>
-      <c r="H28" t="str">
-        <v>${r2_admin_variant} = 'var2'</v>
+        <v>r2_v1_admin_photo</v>
+      </c>
+      <c r="C28" t="str" xml:space="preserve">
+        <v xml:space="preserve">📸 Upload Photo of Count to Unlock Station (MANDATORY)
+Photo upload is mandatory</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Take a clear photo of your team at the station.</v>
+      </c>
+      <c r="E28" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F28" t="str">
+        <v>❌ Station photo upload is mandatory.</v>
+      </c>
+      <c r="I28" t="str">
+        <v>${r2_v1_q1_chess} = 5 and ${r2_v1_q2_uno} = 7 and ${r2_v1_q3_appy} = 3 and ${r2_v1_q4_smoodh} = 4 and ${r2_v1_q5_files} = 2</v>
       </c>
     </row>
     <row r="29" xml:space="preserve">
       <c r="A29" t="str">
+        <v>text</v>
+      </c>
+      <c r="B29" t="str">
+        <v>r2_v1_code</v>
+      </c>
+      <c r="C29" t="str" xml:space="preserve">
+        <v xml:space="preserve">Enter Volunteer Clearance Code (MANDATORY)
+Enter code in caps</v>
+      </c>
+      <c r="D29" t="str">
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+      </c>
+      <c r="E29" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F29" t="str">
+        <v>❌ Volunteer clearance code is mandatory.</v>
+      </c>
+      <c r="G29" t="str">
+        <v>regex(., '^[A-Z0-9\-_]+$') and normalize-space(.) = 'ADM-DUCK-3'</v>
+      </c>
+      <c r="H29" t="str">
+        <v>❌ Incorrect clearance code. Enter the code in UPPERCASE (CAPS ONLY) provided by the volunteer.</v>
+      </c>
+      <c r="I29" t="str">
+        <v>${r2_v1_q1_chess} = 5 and ${r2_v1_q2_uno} = 7 and ${r2_v1_q3_appy} = 3 and ${r2_v1_q4_smoodh} = 4 and ${r2_v1_q5_files} = 2</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>end_group</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>begin_group</v>
+      </c>
+      <c r="B31" t="str">
+        <v>admin_v2_group</v>
+      </c>
+      <c r="C31" t="str">
+        <v>VARIANT B — MEMORY ROOM</v>
+      </c>
+      <c r="I31" t="str">
+        <v>${r2_admin_variant} = 'var2'</v>
+      </c>
+    </row>
+    <row r="32" xml:space="preserve">
+      <c r="A32" t="str">
         <v>note</v>
       </c>
-      <c r="B29" t="str">
+      <c r="B32" t="str">
         <v>admin_v2_intro</v>
       </c>
-      <c r="C29" t="str" xml:space="preserve">
+      <c r="C32" t="str" xml:space="preserve">
         <v xml:space="preserve">🧠 MINI-CHALLENGE: MEMORY ROOM
-Observe the decorated classroom and its details for 20 seconds. Then leave the room and answer the volunteer questions based on memory.
-Enter code in caps</v>
-      </c>
-      <c r="D29" t="str">
-        <v>Complete memory questions with volunteer.</v>
-      </c>
-    </row>
-    <row r="30" xml:space="preserve">
-      <c r="A30" t="str">
-        <v>image</v>
-      </c>
-      <c r="B30" t="str">
-        <v>r2_v2_admin_photo</v>
-      </c>
-      <c r="C30" t="str" xml:space="preserve">
-        <v xml:space="preserve">📸 Upload Photo of Memory Room Challenge
-Photo upload is mandatory</v>
-      </c>
-      <c r="D30" t="str">
-        <v>Take a clear photo of your team at the station.</v>
-      </c>
-      <c r="E30" t="str">
-        <v>yes</v>
-      </c>
-    </row>
-    <row r="31" xml:space="preserve">
-      <c r="A31" t="str">
+You will enter a decorated classroom and observe the room for approximately 20 seconds. You may not record or photograph the room. After leaving, answer the questions from memory.
+Enter code in caps</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Answer all 7 memory questions in CAPS.</v>
+      </c>
+    </row>
+    <row r="33" xml:space="preserve">
+      <c r="A33" t="str">
         <v>text</v>
       </c>
-      <c r="B31" t="str">
-        <v>r2_v2_code</v>
-      </c>
-      <c r="C31" t="str" xml:space="preserve">
-        <v xml:space="preserve">Enter Volunteer Clearance Code
-Enter code in caps</v>
-      </c>
-      <c r="D31" t="str">
+      <c r="B33" t="str">
+        <v>r2_v2_q1_id</v>
+      </c>
+      <c r="C33" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. What colour was the ID card hanging in the classroom? (MANDATORY)
+Enter code in caps</v>
+      </c>
+      <c r="D33" t="str">
         <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
       </c>
-      <c r="E31" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F31" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ADM-DISNEY-3'</v>
-      </c>
-      <c r="G31" t="str">
-        <v>❌ Incorrect code. Enter ADM-DISNEY-3 in CAPS provided by the volunteer.</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="str">
-        <v>end_group</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="str">
-        <v>end_group</v>
+      <c r="E33" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F33" t="str">
+        <v>❌ Question 1 is mandatory.</v>
+      </c>
+      <c r="G33" t="str">
+        <v>regex(., '^[A-Z]+$') and normalize-space(.) = 'RED'</v>
+      </c>
+      <c r="H33" t="str">
+        <v>❌ Incorrect colour. Please enter in UPPERCASE (CAPS ONLY).</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>begin_group</v>
+        <v>select_one clock_time_choices</v>
       </c>
       <c r="B34" t="str">
-        <v>r3_ece_block_group</v>
+        <v>r2_v2_q2_clock</v>
       </c>
       <c r="C34" t="str">
-        <v>ROUND 3 LOCATION CLUE</v>
+        <v>2. What time was shown on the classroom clock? (MANDATORY)</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Select the correct time observed on the clock.</v>
+      </c>
+      <c r="E34" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F34" t="str">
+        <v>❌ Question 2 is mandatory.</v>
+      </c>
+      <c r="G34" t="str">
+        <v>. = 't_1015' or . = 't_1200' or . = 't_0230' or . = 't_0445'</v>
       </c>
       <c r="H34" t="str">
-        <v>${team_name} != '' and ${team_id} != '' and ${team_start_photo} != '' and translate(normalize-space(${r1_mba_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ENG-KID-119' and ${r1_mba_photo} != '' and (translate(normalize-space(${r2_admin_block_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ADMIN' or translate(normalize-space(${r2_admin_block_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ADMIN BLOCK') and translate(normalize-space(${r2_admin_start_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ADMIN-START' and ((${r2_admin_variant} = 'var1' and translate(normalize-space(${r2_v1_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ADM-DUCK-3' and ${r2_v1_admin_photo} != '') or (${r2_admin_variant} = 'var2' and translate(normalize-space(${r2_v2_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ADM-DISNEY-3' and ${r2_v2_admin_photo} != ''))</v>
+        <v>❌ Please select an option.</v>
       </c>
     </row>
     <row r="35" xml:space="preserve">
       <c r="A35" t="str">
+        <v>text</v>
+      </c>
+      <c r="B35" t="str">
+        <v>r2_v2_q3_toy</v>
+      </c>
+      <c r="C35" t="str" xml:space="preserve">
+        <v xml:space="preserve">3. What stuffed toy was present in the classroom? (MANDATORY)
+Enter code in caps</v>
+      </c>
+      <c r="D35" t="str">
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+      </c>
+      <c r="E35" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F35" t="str">
+        <v>❌ Question 3 is mandatory.</v>
+      </c>
+      <c r="G35" t="str">
+        <v>regex(., '^[A-Z ]+$') and normalize-space(.) = 'MANGO'</v>
+      </c>
+      <c r="H35" t="str">
+        <v>❌ Incorrect answer. Please enter in UPPERCASE (CAPS ONLY).</v>
+      </c>
+    </row>
+    <row r="36" xml:space="preserve">
+      <c r="A36" t="str">
+        <v>text</v>
+      </c>
+      <c r="B36" t="str">
+        <v>r2_v2_q4_poster</v>
+      </c>
+      <c r="C36" t="str" xml:space="preserve">
+        <v xml:space="preserve">4. What movie poster was pasted on the wall? (MANDATORY)
+Enter code in caps</v>
+      </c>
+      <c r="D36" t="str">
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+      </c>
+      <c r="E36" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F36" t="str">
+        <v>❌ Question 4 is mandatory.</v>
+      </c>
+      <c r="G36" t="str">
+        <v>regex(., '^[A-Z0-9\- ]+$') and (normalize-space(.) = 'SPIDER MAN BRAND NEW DAY' or normalize-space(.) = 'SPIDER-MAN BRAND NEW DAY' or normalize-space(.) = 'SPIDERMAN BRAND NEW DAY' or normalize-space(.) = 'SPIDER MAN')</v>
+      </c>
+      <c r="H36" t="str">
+        <v>❌ Incorrect movie poster name. Please enter in UPPERCASE (CAPS ONLY).</v>
+      </c>
+    </row>
+    <row r="37" xml:space="preserve">
+      <c r="A37" t="str">
+        <v>text</v>
+      </c>
+      <c r="B37" t="str">
+        <v>r2_v2_q5_novel</v>
+      </c>
+      <c r="C37" t="str" xml:space="preserve">
+        <v xml:space="preserve">5. Name of the novel present on the ground? (MANDATORY)
+Enter code in caps</v>
+      </c>
+      <c r="D37" t="str">
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+      </c>
+      <c r="E37" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F37" t="str">
+        <v>❌ Question 5 is mandatory.</v>
+      </c>
+      <c r="G37" t="str">
+        <v>regex(., '^[A-Z ]+$') and normalize-space(.) = 'ATOMIC HABITS'</v>
+      </c>
+      <c r="H37" t="str">
+        <v>❌ Incorrect novel name. Please enter in UPPERCASE (CAPS ONLY).</v>
+      </c>
+    </row>
+    <row r="38" xml:space="preserve">
+      <c r="A38" t="str">
+        <v>text</v>
+      </c>
+      <c r="B38" t="str">
+        <v>r2_v2_q6_board</v>
+      </c>
+      <c r="C38" t="str" xml:space="preserve">
+        <v xml:space="preserve">6. What was written on the classroom board? (MANDATORY)
+Enter code in caps</v>
+      </c>
+      <c r="D38" t="str">
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+      </c>
+      <c r="E38" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F38" t="str">
+        <v>❌ Question 6 is mandatory.</v>
+      </c>
+      <c r="G38" t="str">
+        <v>regex(., '^[A-Z ]+$') and (normalize-space(.) = 'PYTHAGORAS THEOREM' or normalize-space(.) = 'PYTHAGOREAN THEOREM')</v>
+      </c>
+      <c r="H38" t="str">
+        <v>❌ Incorrect board text. Please enter in UPPERCASE (CAPS ONLY).</v>
+      </c>
+    </row>
+    <row r="39" xml:space="preserve">
+      <c r="A39" t="str">
+        <v>text</v>
+      </c>
+      <c r="B39" t="str">
+        <v>r2_v2_q7_benches</v>
+      </c>
+      <c r="C39" t="str" xml:space="preserve">
+        <v xml:space="preserve">7. What object was placed on the benches? (MANDATORY)
+Enter code in caps</v>
+      </c>
+      <c r="D39" t="str">
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+      </c>
+      <c r="E39" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F39" t="str">
+        <v>❌ Question 7 is mandatory.</v>
+      </c>
+      <c r="G39" t="str">
+        <v>regex(., '^[A-Z ]+$') and (normalize-space(.) = 'TABLE TENNIS' or normalize-space(.) = 'TABLE TENNIS RACKET' or normalize-space(.) = 'TABLE TENNIS BALL' or normalize-space(.) = 'TT RACKET')</v>
+      </c>
+      <c r="H39" t="str">
+        <v>❌ Incorrect object name. Please enter in UPPERCASE (CAPS ONLY).</v>
+      </c>
+    </row>
+    <row r="40" xml:space="preserve">
+      <c r="A40" t="str">
         <v>note</v>
       </c>
-      <c r="B35" t="str">
+      <c r="B40" t="str">
+        <v>r2_v2_success_note</v>
+      </c>
+      <c r="C40" t="str" xml:space="preserve">
+        <v xml:space="preserve">🎉 Memory challenge cleared. Enter the challenge code from volunteer to continue.
+Enter code in caps</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Ask volunteer for challenge code.</v>
+      </c>
+      <c r="I40" t="str">
+        <v>normalize-space(${r2_v2_q1_id}) = 'RED' and ${r2_v2_q2_clock} != '' and normalize-space(${r2_v2_q3_toy}) = 'MANGO' and (normalize-space(${r2_v2_q4_poster}) = 'SPIDER MAN BRAND NEW DAY' or normalize-space(${r2_v2_q4_poster}) = 'SPIDER-MAN BRAND NEW DAY' or normalize-space(${r2_v2_q4_poster}) = 'SPIDERMAN BRAND NEW DAY' or normalize-space(${r2_v2_q4_poster}) = 'SPIDER MAN') and normalize-space(${r2_v2_q5_novel}) = 'ATOMIC HABITS' and (normalize-space(${r2_v2_q6_board}) = 'PYTHAGORAS THEOREM' or normalize-space(${r2_v2_q6_board}) = 'PYTHAGOREAN THEOREM') and (normalize-space(${r2_v2_q7_benches}) = 'TABLE TENNIS' or normalize-space(${r2_v2_q7_benches}) = 'TABLE TENNIS RACKET' or normalize-space(${r2_v2_q7_benches}) = 'TABLE TENNIS BALL' or normalize-space(${r2_v2_q7_benches}) = 'TT RACKET')</v>
+      </c>
+    </row>
+    <row r="41" xml:space="preserve">
+      <c r="A41" t="str">
+        <v>image</v>
+      </c>
+      <c r="B41" t="str">
+        <v>r2_v2_admin_photo</v>
+      </c>
+      <c r="C41" t="str" xml:space="preserve">
+        <v xml:space="preserve">📸 Upload Photo of Memory Room Challenge (MANDATORY)
+Photo upload is mandatory</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Take a clear photo of your team at the station.</v>
+      </c>
+      <c r="E41" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F41" t="str">
+        <v>❌ Station photo upload is mandatory.</v>
+      </c>
+      <c r="I41" t="str">
+        <v>normalize-space(${r2_v2_q1_id}) = 'RED' and ${r2_v2_q2_clock} != '' and normalize-space(${r2_v2_q3_toy}) = 'MANGO' and (normalize-space(${r2_v2_q4_poster}) = 'SPIDER MAN BRAND NEW DAY' or normalize-space(${r2_v2_q4_poster}) = 'SPIDER-MAN BRAND NEW DAY' or normalize-space(${r2_v2_q4_poster}) = 'SPIDERMAN BRAND NEW DAY' or normalize-space(${r2_v2_q4_poster}) = 'SPIDER MAN') and normalize-space(${r2_v2_q5_novel}) = 'ATOMIC HABITS' and (normalize-space(${r2_v2_q6_board}) = 'PYTHAGORAS THEOREM' or normalize-space(${r2_v2_q6_board}) = 'PYTHAGOREAN THEOREM') and (normalize-space(${r2_v2_q7_benches}) = 'TABLE TENNIS' or normalize-space(${r2_v2_q7_benches}) = 'TABLE TENNIS RACKET' or normalize-space(${r2_v2_q7_benches}) = 'TABLE TENNIS BALL' or normalize-space(${r2_v2_q7_benches}) = 'TT RACKET')</v>
+      </c>
+    </row>
+    <row r="42" xml:space="preserve">
+      <c r="A42" t="str">
+        <v>text</v>
+      </c>
+      <c r="B42" t="str">
+        <v>r2_v2_code</v>
+      </c>
+      <c r="C42" t="str" xml:space="preserve">
+        <v xml:space="preserve">Enter Volunteer Clearance Code (MANDATORY)
+Enter code in caps</v>
+      </c>
+      <c r="D42" t="str">
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+      </c>
+      <c r="E42" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F42" t="str">
+        <v>❌ Volunteer clearance code is mandatory.</v>
+      </c>
+      <c r="G42" t="str">
+        <v>regex(., '^[A-Z0-9\-_]+$') and normalize-space(.) = 'ADM-DISNEY-3'</v>
+      </c>
+      <c r="H42" t="str">
+        <v>❌ Incorrect code. Enter ADM-DISNEY-3 in CAPS provided by the volunteer.</v>
+      </c>
+      <c r="I42" t="str">
+        <v>normalize-space(${r2_v2_q1_id}) = 'RED' and ${r2_v2_q2_clock} != '' and normalize-space(${r2_v2_q3_toy}) = 'MANGO' and (normalize-space(${r2_v2_q4_poster}) = 'SPIDER MAN BRAND NEW DAY' or normalize-space(${r2_v2_q4_poster}) = 'SPIDER-MAN BRAND NEW DAY' or normalize-space(${r2_v2_q4_poster}) = 'SPIDERMAN BRAND NEW DAY' or normalize-space(${r2_v2_q4_poster}) = 'SPIDER MAN') and normalize-space(${r2_v2_q5_novel}) = 'ATOMIC HABITS' and (normalize-space(${r2_v2_q6_board}) = 'PYTHAGORAS THEOREM' or normalize-space(${r2_v2_q6_board}) = 'PYTHAGOREAN THEOREM') and (normalize-space(${r2_v2_q7_benches}) = 'TABLE TENNIS' or normalize-space(${r2_v2_q7_benches}) = 'TABLE TENNIS RACKET' or normalize-space(${r2_v2_q7_benches}) = 'TABLE TENNIS BALL' or normalize-space(${r2_v2_q7_benches}) = 'TT RACKET')</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>end_group</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>end_group</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>begin_group</v>
+      </c>
+      <c r="B45" t="str">
+        <v>r3_ece_block_group</v>
+      </c>
+      <c r="C45" t="str">
+        <v>ROUND 3 LOCATION CLUE</v>
+      </c>
+      <c r="I45" t="str">
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_mba_code}) = 'ENG-KID-119' and ${r1_mba_photo} != '' and (normalize-space(${r2_admin_block_answer}) = 'ADMIN' or normalize-space(${r2_admin_block_answer}) = 'ADMIN BLOCK') and normalize-space(${r2_admin_start_code}) = 'ADMIN-START' and ((${r2_admin_variant} = 'var1' and normalize-space(${r2_v1_code}) = 'ADM-DUCK-3' and ${r2_v1_admin_photo} != '') or (${r2_admin_variant} = 'var2' and normalize-space(${r2_v2_code}) = 'ADM-DISNEY-3' and ${r2_v2_admin_photo} != ''))</v>
+      </c>
+    </row>
+    <row r="46" xml:space="preserve">
+      <c r="A46" t="str">
+        <v>note</v>
+      </c>
+      <c r="B46" t="str">
         <v>r3_ece_riddle_note</v>
       </c>
-      <c r="C35" t="str" xml:space="preserve">
-        <v xml:space="preserve">📍 ROUND 3 LOCATION CLUE: ELECTRONICS RIDDLE
+      <c r="C46" t="str" xml:space="preserve">
+        <v xml:space="preserve">📍 ROUND 3 LOCATION CLUE
 "I deal in waves, both low and high,
 Where analog signals never lie.
 With resistors, chips, and wires in place,
 Find your next clue in this circuit space."
 Enter code in caps</v>
       </c>
-      <c r="D35" t="str">
-        <v>Solve the riddle to deduce the destination block.</v>
-      </c>
-    </row>
-    <row r="36" xml:space="preserve">
-      <c r="A36" t="str">
+      <c r="D46" t="str">
+        <v>Solve the riddle to discover your next location.</v>
+      </c>
+    </row>
+    <row r="47" xml:space="preserve">
+      <c r="A47" t="str">
         <v>text</v>
       </c>
-      <c r="B36" t="str">
+      <c r="B47" t="str">
         <v>r3_ece_block_answer</v>
       </c>
-      <c r="C36" t="str" xml:space="preserve">
-        <v xml:space="preserve">Which campus block does this circuit riddle direct your team to?
-Enter code in caps</v>
-      </c>
-      <c r="D36" t="str">
+      <c r="C47" t="str" xml:space="preserve">
+        <v xml:space="preserve">Enter your deduced destination location: (MANDATORY)
+Enter code in caps</v>
+      </c>
+      <c r="D47" t="str">
         <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
       </c>
-      <c r="E36" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F36" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ECE' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ECE BLOCK'</v>
-      </c>
-      <c r="G36" t="str">
-        <v>❌ Incorrect destination. Read the riddle and enter the block name in CAPS.</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="str">
+      <c r="E47" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F47" t="str">
+        <v>❌ Destination location is mandatory.</v>
+      </c>
+      <c r="G47" t="str">
+        <v>regex(., '^[A-Z ]+$') and (normalize-space(.) = 'ECE' or normalize-space(.) = 'ECE BLOCK')</v>
+      </c>
+      <c r="H47" t="str">
+        <v>❌ Not quite. Think about the department described by the electronics-related clues.</v>
+      </c>
+    </row>
+    <row r="48" xml:space="preserve">
+      <c r="A48" t="str">
+        <v>note</v>
+      </c>
+      <c r="B48" t="str">
+        <v>r3_ece_proceed_note</v>
+      </c>
+      <c r="C48" t="str" xml:space="preserve">
+        <v xml:space="preserve">🏃 Correct! Proceed to your next location and look for the next challenge.
+Enter code in caps</v>
+      </c>
+      <c r="D48" t="str">
+        <v>Proceed to the location for the QR hunt.</v>
+      </c>
+      <c r="I48" t="str">
+        <v>normalize-space(${r3_ece_block_answer}) = 'ECE' or normalize-space(${r3_ece_block_answer}) = 'ECE BLOCK'</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
         <v>end_group</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="str">
+    <row r="50">
+      <c r="A50" t="str">
         <v>begin_group</v>
       </c>
-      <c r="B38" t="str">
-        <v>ece_arrival_group</v>
-      </c>
-      <c r="C38" t="str">
-        <v>ECE ARRIVAL</v>
-      </c>
-      <c r="H38" t="str">
-        <v>${team_name} != '' and ${team_id} != '' and ${team_start_photo} != '' and translate(normalize-space(${r1_mba_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ENG-KID-119' and ${r1_mba_photo} != '' and (translate(normalize-space(${r2_admin_block_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ADMIN' or translate(normalize-space(${r2_admin_block_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ADMIN BLOCK') and translate(normalize-space(${r2_admin_start_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ADMIN-START' and ((${r2_admin_variant} = 'var1' and translate(normalize-space(${r2_v1_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ADM-DUCK-3' and ${r2_v1_admin_photo} != '') or (${r2_admin_variant} = 'var2' and translate(normalize-space(${r2_v2_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ADM-DISNEY-3' and ${r2_v2_admin_photo} != '')) and (translate(normalize-space(${r3_ece_block_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ECE' or translate(normalize-space(${r3_ece_block_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ECE BLOCK')</v>
-      </c>
-    </row>
-    <row r="39" xml:space="preserve">
-      <c r="A39" t="str">
+      <c r="B50" t="str">
+        <v>r3_ece_qr_group</v>
+      </c>
+      <c r="C50" t="str">
+        <v>ROUND 3 — QR HUNT</v>
+      </c>
+      <c r="I50" t="str">
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_mba_code}) = 'ENG-KID-119' and ${r1_mba_photo} != '' and (normalize-space(${r2_admin_block_answer}) = 'ADMIN' or normalize-space(${r2_admin_block_answer}) = 'ADMIN BLOCK') and normalize-space(${r2_admin_start_code}) = 'ADMIN-START' and ((${r2_admin_variant} = 'var1' and normalize-space(${r2_v1_code}) = 'ADM-DUCK-3' and ${r2_v1_admin_photo} != '') or (${r2_admin_variant} = 'var2' and normalize-space(${r2_v2_code}) = 'ADM-DISNEY-3' and ${r2_v2_admin_photo} != '')) and (normalize-space(${r3_ece_block_answer}) = 'ECE' or normalize-space(${r3_ece_block_answer}) = 'ECE BLOCK')</v>
+      </c>
+    </row>
+    <row r="51" xml:space="preserve">
+      <c r="A51" t="str">
         <v>note</v>
       </c>
-      <c r="B39" t="str">
-        <v>ece_arrival_note</v>
-      </c>
-      <c r="C39" t="str" xml:space="preserve">
-        <v xml:space="preserve">🏃 PROCEED TO ECE BLOCK
-Report immediately to the ECE station and meet the volunteer to receive your ECE start code.
-Enter code in caps</v>
-      </c>
-      <c r="D39" t="str">
-        <v>Meet volunteer at ECE station.</v>
-      </c>
-    </row>
-    <row r="40" xml:space="preserve">
-      <c r="A40" t="str">
-        <v>text</v>
-      </c>
-      <c r="B40" t="str">
-        <v>r3_ece_start_code</v>
-      </c>
-      <c r="C40" t="str" xml:space="preserve">
-        <v xml:space="preserve">Enter ECE Volunteer Start Code
-Enter code in caps</v>
-      </c>
-      <c r="D40" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
-      </c>
-      <c r="E40" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F40" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ECE-LETSGO'</v>
-      </c>
-      <c r="G40" t="str">
-        <v>❌ Incorrect code. Enter ECE-LETSGO in CAPS provided by the ECE volunteer.</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="str">
-        <v>end_group</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="str">
-        <v>begin_group</v>
-      </c>
-      <c r="B42" t="str">
-        <v>r3_ece_qr_group</v>
-      </c>
-      <c r="C42" t="str">
-        <v>ROUND 3 — QR HUNT</v>
-      </c>
-      <c r="H42" t="str">
-        <v>${team_name} != '' and ${team_id} != '' and ${team_start_photo} != '' and translate(normalize-space(${r1_mba_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ENG-KID-119' and ${r1_mba_photo} != '' and (translate(normalize-space(${r2_admin_block_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ADMIN' or translate(normalize-space(${r2_admin_block_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ADMIN BLOCK') and translate(normalize-space(${r2_admin_start_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ADMIN-START' and ((${r2_admin_variant} = 'var1' and translate(normalize-space(${r2_v1_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ADM-DUCK-3' and ${r2_v1_admin_photo} != '') or (${r2_admin_variant} = 'var2' and translate(normalize-space(${r2_v2_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ADM-DISNEY-3' and ${r2_v2_admin_photo} != '')) and (translate(normalize-space(${r3_ece_block_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ECE' or translate(normalize-space(${r3_ece_block_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ECE BLOCK') and translate(normalize-space(${r3_ece_start_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ECE-LETSGO'</v>
-      </c>
-    </row>
-    <row r="43" xml:space="preserve">
-      <c r="A43" t="str">
-        <v>note</v>
-      </c>
-      <c r="B43" t="str">
+      <c r="B51" t="str">
         <v>r3_ece_qr_note</v>
       </c>
-      <c r="C43" t="str" xml:space="preserve">
+      <c r="C51" t="str" xml:space="preserve">
         <v xml:space="preserve">📍 ROUND 3: QR HUNT
 Search the location physically to locate the hidden QR code.
 Scan the QR code using the scanner below.
 Enter code in caps</v>
       </c>
-      <c r="D43" t="str">
+      <c r="D51" t="str">
         <v>Locate and scan the hidden QR code.</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="str">
+    <row r="52">
+      <c r="A52" t="str">
         <v>barcode</v>
       </c>
-      <c r="B44" t="str">
+      <c r="B52" t="str">
         <v>r3_ece_qr_scan</v>
       </c>
-      <c r="C44" t="str">
-        <v>Scan Discovered QR Code</v>
-      </c>
-      <c r="D44" t="str">
+      <c r="C52" t="str">
+        <v>Scan Discovered QR Code (MANDATORY)</v>
+      </c>
+      <c r="D52" t="str">
         <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
       </c>
-      <c r="E44" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F44" t="str">
-        <v>normalize-space(.) = 'HARRY_POTTER' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'HARRY_POTTER'</v>
-      </c>
-      <c r="G44" t="str">
-        <v>❌ Incorrect QR code scanned. Search for the correct QR code at this station.</v>
-      </c>
-    </row>
-    <row r="45" xml:space="preserve">
-      <c r="A45" t="str">
-        <v>image</v>
-      </c>
-      <c r="B45" t="str">
-        <v>r3_ece_qr_photo</v>
-      </c>
-      <c r="C45" t="str" xml:space="preserve">
-        <v xml:space="preserve">📸 Upload Photo of Discovered QR Code / Station
-Photo upload is mandatory</v>
-      </c>
-      <c r="D45" t="str">
-        <v>Take a clear photo of the discovered QR code location.</v>
-      </c>
-      <c r="E45" t="str">
-        <v>yes</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="str">
-        <v>end_group</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="str">
-        <v>begin_group</v>
-      </c>
-      <c r="B47" t="str">
-        <v>r4_lib_cipher_group</v>
-      </c>
-      <c r="C47" t="str">
-        <v>ROUND 4 LOCATION CLUE</v>
-      </c>
-      <c r="H47" t="str">
-        <v>${team_name} != '' and ${team_id} != '' and ${team_start_photo} != '' and translate(normalize-space(${r1_mba_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ENG-KID-119' and ${r1_mba_photo} != '' and (translate(normalize-space(${r2_admin_block_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ADMIN' or translate(normalize-space(${r2_admin_block_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ADMIN BLOCK') and translate(normalize-space(${r2_admin_start_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ADMIN-START' and ((${r2_admin_variant} = 'var1' and translate(normalize-space(${r2_v1_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ADM-DUCK-3' and ${r2_v1_admin_photo} != '') or (${r2_admin_variant} = 'var2' and translate(normalize-space(${r2_v2_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ADM-DISNEY-3' and ${r2_v2_admin_photo} != '')) and (translate(normalize-space(${r3_ece_block_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ECE' or translate(normalize-space(${r3_ece_block_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ECE BLOCK') and translate(normalize-space(${r3_ece_start_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ECE-LETSGO' and (normalize-space(${r3_ece_qr_scan}) = 'HARRY_POTTER' or translate(normalize-space(${r3_ece_qr_scan}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'HARRY_POTTER') and ${r3_ece_qr_photo} != ''</v>
-      </c>
-    </row>
-    <row r="48" xml:space="preserve">
-      <c r="A48" t="str">
-        <v>note</v>
-      </c>
-      <c r="B48" t="str">
-        <v>r4_lib_cipher_note</v>
-      </c>
-      <c r="C48" t="str" xml:space="preserve">
-        <v xml:space="preserve">🔐 ROUND 4 LOCATION CLUE: CAESAR CIPHER
-Decode the encrypted message by moving each letter 3 steps backward in the alphabet to reveal your next destination!
-📜 CIPHER INSTRUCTION:
-"OLEUDUB — Julius Caesar would have understood this. You probably won't — until you move every letter three steps backward. Decode the message. Your answer is where the next clue waits."
-Example Shift Rule (-3):
-• D → A
-• G → D
-• M → J
-• Z → W
-Enter code in caps</v>
-      </c>
-      <c r="D48" t="str">
-        <v>Move each letter 3 steps backward.</v>
-      </c>
-    </row>
-    <row r="49" xml:space="preserve">
-      <c r="A49" t="str">
-        <v>text</v>
-      </c>
-      <c r="B49" t="str">
-        <v>r4_lib_cipher_answer</v>
-      </c>
-      <c r="C49" t="str" xml:space="preserve">
-        <v xml:space="preserve">Decode Encrypted Message [ OLEUDUB ]:
-Enter code in caps</v>
-      </c>
-      <c r="D49" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
-      </c>
-      <c r="E49" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F49" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'LIBRARY' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CENTRAL LIBRARY'</v>
-      </c>
-      <c r="G49" t="str">
-        <v>❌ Incorrect destination. Decode OLEUDUB by shifting each letter 3 steps backward.</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="str">
-        <v>end_group</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="str">
-        <v>begin_group</v>
-      </c>
-      <c r="B51" t="str">
-        <v>lib_arrival_group</v>
-      </c>
-      <c r="C51" t="str">
-        <v>LIBRARY ARRIVAL</v>
-      </c>
-      <c r="H51" t="str">
-        <v>${team_name} != '' and ${team_id} != '' and ${team_start_photo} != '' and translate(normalize-space(${r1_mba_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ENG-KID-119' and ${r1_mba_photo} != '' and (translate(normalize-space(${r2_admin_block_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ADMIN' or translate(normalize-space(${r2_admin_block_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ADMIN BLOCK') and translate(normalize-space(${r2_admin_start_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ADMIN-START' and ((${r2_admin_variant} = 'var1' and translate(normalize-space(${r2_v1_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ADM-DUCK-3' and ${r2_v1_admin_photo} != '') or (${r2_admin_variant} = 'var2' and translate(normalize-space(${r2_v2_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ADM-DISNEY-3' and ${r2_v2_admin_photo} != '')) and (translate(normalize-space(${r3_ece_block_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ECE' or translate(normalize-space(${r3_ece_block_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ECE BLOCK') and translate(normalize-space(${r3_ece_start_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ECE-LETSGO' and (normalize-space(${r3_ece_qr_scan}) = 'HARRY_POTTER' or translate(normalize-space(${r3_ece_qr_scan}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'HARRY_POTTER') and ${r3_ece_qr_photo} != '' and (translate(normalize-space(${r4_lib_cipher_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'LIBRARY' or translate(normalize-space(${r4_lib_cipher_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CENTRAL LIBRARY')</v>
-      </c>
-    </row>
-    <row r="52" xml:space="preserve">
-      <c r="A52" t="str">
-        <v>note</v>
-      </c>
-      <c r="B52" t="str">
-        <v>lib_arrival_note</v>
-      </c>
-      <c r="C52" t="str" xml:space="preserve">
-        <v xml:space="preserve">🏃 PROCEED TO LIBRARY
-Report immediately to the Library station and meet the volunteer to receive your arrival verification code.
-Enter code in caps</v>
-      </c>
-      <c r="D52" t="str">
-        <v>Meet volunteer at Library station.</v>
+      <c r="E52" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F52" t="str">
+        <v>❌ QR code scanning is mandatory.</v>
+      </c>
+      <c r="G52" t="str">
+        <v>normalize-space(.) = 'HARRY_POTTER'</v>
+      </c>
+      <c r="H52" t="str">
+        <v>❌ Incorrect code. Continue the QR hunt and check the code carefully.</v>
       </c>
     </row>
     <row r="53" xml:space="preserve">
       <c r="A53" t="str">
-        <v>text</v>
+        <v>image</v>
       </c>
       <c r="B53" t="str">
-        <v>r4_lib_start_code</v>
+        <v>r3_ece_qr_photo</v>
       </c>
       <c r="C53" t="str" xml:space="preserve">
-        <v xml:space="preserve">Enter Library Volunteer Arrival Code
-Enter code in caps</v>
+        <v xml:space="preserve">📸 Upload Photo of Discovered QR Code / Station (MANDATORY)
+Photo upload is mandatory</v>
       </c>
       <c r="D53" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>Take a clear photo of the discovered QR code location.</v>
       </c>
       <c r="E53" t="str">
         <v>yes</v>
       </c>
       <c r="F53" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'TALL-NERD'</v>
-      </c>
-      <c r="G53" t="str">
-        <v>❌ Incorrect code. Enter TALL-NERD in CAPS provided by the Library volunteer.</v>
+        <v>❌ Station photo upload is mandatory.</v>
       </c>
     </row>
     <row r="54">
@@ -1268,13 +1501,13 @@
         <v>begin_group</v>
       </c>
       <c r="B55" t="str">
-        <v>r4_lib_phy_group</v>
+        <v>r4_lib_cipher_group</v>
       </c>
       <c r="C55" t="str">
-        <v>ROUND 4 — PHYSICAL CHALLENGE</v>
-      </c>
-      <c r="H55" t="str">
-        <v>${team_name} != '' and ${team_id} != '' and ${team_start_photo} != '' and translate(normalize-space(${r1_mba_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ENG-KID-119' and ${r1_mba_photo} != '' and (translate(normalize-space(${r2_admin_block_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ADMIN' or translate(normalize-space(${r2_admin_block_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ADMIN BLOCK') and translate(normalize-space(${r2_admin_start_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ADMIN-START' and ((${r2_admin_variant} = 'var1' and translate(normalize-space(${r2_v1_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ADM-DUCK-3' and ${r2_v1_admin_photo} != '') or (${r2_admin_variant} = 'var2' and translate(normalize-space(${r2_v2_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ADM-DISNEY-3' and ${r2_v2_admin_photo} != '')) and (translate(normalize-space(${r3_ece_block_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ECE' or translate(normalize-space(${r3_ece_block_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ECE BLOCK') and translate(normalize-space(${r3_ece_start_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ECE-LETSGO' and (normalize-space(${r3_ece_qr_scan}) = 'HARRY_POTTER' or translate(normalize-space(${r3_ece_qr_scan}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'HARRY_POTTER') and ${r3_ece_qr_photo} != '' and (translate(normalize-space(${r4_lib_cipher_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'LIBRARY' or translate(normalize-space(${r4_lib_cipher_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CENTRAL LIBRARY') and translate(normalize-space(${r4_lib_start_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'TALL-NERD'</v>
+        <v>ROUND 4 LOCATION CLUE</v>
+      </c>
+      <c r="I55" t="str">
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_mba_code}) = 'ENG-KID-119' and ${r1_mba_photo} != '' and (normalize-space(${r2_admin_block_answer}) = 'ADMIN' or normalize-space(${r2_admin_block_answer}) = 'ADMIN BLOCK') and normalize-space(${r2_admin_start_code}) = 'ADMIN-START' and ((${r2_admin_variant} = 'var1' and normalize-space(${r2_v1_code}) = 'ADM-DUCK-3' and ${r2_v1_admin_photo} != '') or (${r2_admin_variant} = 'var2' and normalize-space(${r2_v2_code}) = 'ADM-DISNEY-3' and ${r2_v2_admin_photo} != '')) and (normalize-space(${r3_ece_block_answer}) = 'ECE' or normalize-space(${r3_ece_block_answer}) = 'ECE BLOCK') and normalize-space(${r3_ece_qr_scan}) = 'HARRY_POTTER' and ${r3_ece_qr_photo} != ''</v>
       </c>
     </row>
     <row r="56" xml:space="preserve">
@@ -1282,212 +1515,221 @@
         <v>note</v>
       </c>
       <c r="B56" t="str">
+        <v>r4_lib_cipher_note</v>
+      </c>
+      <c r="C56" t="str" xml:space="preserve">
+        <v xml:space="preserve">🔐 ROUND 4 LOCATION CLUE: CAESAR CIPHER
+"Julius Caesar would have understood this.
+Every letter has been shifted three places.
+Move every letter three steps backward and decode the message.
+Your answer is where the next clue waits."
+Cipher:
+OLEUDUB
+Enter code in caps</v>
+      </c>
+      <c r="D56" t="str">
+        <v>Shift every letter 3 places backward.</v>
+      </c>
+    </row>
+    <row r="57" xml:space="preserve">
+      <c r="A57" t="str">
+        <v>text</v>
+      </c>
+      <c r="B57" t="str">
+        <v>r4_lib_cipher_answer</v>
+      </c>
+      <c r="C57" t="str" xml:space="preserve">
+        <v xml:space="preserve">Enter your decoded destination location: (MANDATORY)
+Enter code in caps</v>
+      </c>
+      <c r="D57" t="str">
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+      </c>
+      <c r="E57" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F57" t="str">
+        <v>❌ Destination location is mandatory.</v>
+      </c>
+      <c r="G57" t="str">
+        <v>regex(., '^[A-Z ]+$') and (normalize-space(.) = 'LIBRARY' or normalize-space(.) = 'CENTRAL LIBRARY')</v>
+      </c>
+      <c r="H57" t="str">
+        <v>❌ Incorrect. Remember that every letter must be shifted three places backward.</v>
+      </c>
+    </row>
+    <row r="58" xml:space="preserve">
+      <c r="A58" t="str">
+        <v>note</v>
+      </c>
+      <c r="B58" t="str">
+        <v>r4_lib_proceed_note</v>
+      </c>
+      <c r="C58" t="str" xml:space="preserve">
+        <v xml:space="preserve">🏃 Correct! Proceed to your next location and look for the physical challenge.
+Enter code in caps</v>
+      </c>
+      <c r="D58" t="str">
+        <v>Proceed to the location and ask volunteer for arrival code.</v>
+      </c>
+      <c r="I58" t="str">
+        <v>normalize-space(${r4_lib_cipher_answer}) = 'LIBRARY' or normalize-space(${r4_lib_cipher_answer}) = 'CENTRAL LIBRARY'</v>
+      </c>
+    </row>
+    <row r="59" xml:space="preserve">
+      <c r="A59" t="str">
+        <v>text</v>
+      </c>
+      <c r="B59" t="str">
+        <v>r4_lib_start_code</v>
+      </c>
+      <c r="C59" t="str" xml:space="preserve">
+        <v xml:space="preserve">Enter Arrival Code from Volunteer (MANDATORY)
+Enter code in caps</v>
+      </c>
+      <c r="D59" t="str">
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+      </c>
+      <c r="E59" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F59" t="str">
+        <v>❌ Arrival code is mandatory.</v>
+      </c>
+      <c r="G59" t="str">
+        <v>regex(., '^[A-Z0-9\-_]+$') and normalize-space(.) = 'TALL-NERD'</v>
+      </c>
+      <c r="H59" t="str">
+        <v>❌ Incorrect code. Enter TALL-NERD in CAPS provided by the volunteer.</v>
+      </c>
+      <c r="I59" t="str">
+        <v>normalize-space(${r4_lib_cipher_answer}) = 'LIBRARY' or normalize-space(${r4_lib_cipher_answer}) = 'CENTRAL LIBRARY'</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>end_group</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>begin_group</v>
+      </c>
+      <c r="B61" t="str">
+        <v>r4_lib_phy_group</v>
+      </c>
+      <c r="C61" t="str">
+        <v>ROUND 4 — PHYSICAL CHALLENGE</v>
+      </c>
+      <c r="I61" t="str">
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_mba_code}) = 'ENG-KID-119' and ${r1_mba_photo} != '' and (normalize-space(${r2_admin_block_answer}) = 'ADMIN' or normalize-space(${r2_admin_block_answer}) = 'ADMIN BLOCK') and normalize-space(${r2_admin_start_code}) = 'ADMIN-START' and ((${r2_admin_variant} = 'var1' and normalize-space(${r2_v1_code}) = 'ADM-DUCK-3' and ${r2_v1_admin_photo} != '') or (${r2_admin_variant} = 'var2' and normalize-space(${r2_v2_code}) = 'ADM-DISNEY-3' and ${r2_v2_admin_photo} != '')) and (normalize-space(${r3_ece_block_answer}) = 'ECE' or normalize-space(${r3_ece_block_answer}) = 'ECE BLOCK') and normalize-space(${r3_ece_qr_scan}) = 'HARRY_POTTER' and ${r3_ece_qr_photo} != '' and (normalize-space(${r4_lib_cipher_answer}) = 'LIBRARY' or normalize-space(${r4_lib_cipher_answer}) = 'CENTRAL LIBRARY') and normalize-space(${r4_lib_start_code}) = 'TALL-NERD'</v>
+      </c>
+    </row>
+    <row r="62" xml:space="preserve">
+      <c r="A62" t="str">
+        <v>note</v>
+      </c>
+      <c r="B62" t="str">
         <v>r4_lib_phy_note</v>
       </c>
-      <c r="C56" t="str" xml:space="preserve">
+      <c r="C62" t="str" xml:space="preserve">
         <v xml:space="preserve">📍 ROUND 4: PHYSICAL CHALLENGE
 Report to the station and complete the physical challenge under volunteer supervision.
 Enter code in caps</v>
       </c>
-      <c r="D56" t="str">
+      <c r="D62" t="str">
         <v>Complete physical challenge with volunteer.</v>
       </c>
     </row>
-    <row r="57" xml:space="preserve">
-      <c r="A57" t="str">
-        <v>image</v>
-      </c>
-      <c r="B57" t="str">
-        <v>r4_lib_phy_photo</v>
-      </c>
-      <c r="C57" t="str" xml:space="preserve">
-        <v xml:space="preserve">📸 Upload Photo of Physical Challenge Completion
-Photo upload is mandatory</v>
-      </c>
-      <c r="D57" t="str">
-        <v>Take a clear photo of your team completing the physical challenge.</v>
-      </c>
-      <c r="E57" t="str">
-        <v>yes</v>
-      </c>
-    </row>
-    <row r="58" xml:space="preserve">
-      <c r="A58" t="str">
-        <v>text</v>
-      </c>
-      <c r="B58" t="str">
-        <v>r4_lib_phy_code</v>
-      </c>
-      <c r="C58" t="str" xml:space="preserve">
-        <v xml:space="preserve">Enter Volunteer Clearance Code
-Enter code in caps</v>
-      </c>
-      <c r="D58" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
-      </c>
-      <c r="E58" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F58" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'LAST-LEG'</v>
-      </c>
-      <c r="G58" t="str">
-        <v>❌ Incorrect code. Enter LAST-LEG in CAPS provided by the volunteer.</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="str">
-        <v>end_group</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="str">
-        <v>begin_group</v>
-      </c>
-      <c r="B60" t="str">
-        <v>final_puzzles_group</v>
-      </c>
-      <c r="C60" t="str">
-        <v>FINAL PUZZLES</v>
-      </c>
-      <c r="H60" t="str">
-        <v>${team_name} != '' and ${team_id} != '' and ${team_start_photo} != '' and translate(normalize-space(${r1_mba_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ENG-KID-119' and ${r1_mba_photo} != '' and (translate(normalize-space(${r2_admin_block_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ADMIN' or translate(normalize-space(${r2_admin_block_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ADMIN BLOCK') and translate(normalize-space(${r2_admin_start_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ADMIN-START' and ((${r2_admin_variant} = 'var1' and translate(normalize-space(${r2_v1_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ADM-DUCK-3' and ${r2_v1_admin_photo} != '') or (${r2_admin_variant} = 'var2' and translate(normalize-space(${r2_v2_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ADM-DISNEY-3' and ${r2_v2_admin_photo} != '')) and (translate(normalize-space(${r3_ece_block_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ECE' or translate(normalize-space(${r3_ece_block_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ECE BLOCK') and translate(normalize-space(${r3_ece_start_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ECE-LETSGO' and (normalize-space(${r3_ece_qr_scan}) = 'HARRY_POTTER' or translate(normalize-space(${r3_ece_qr_scan}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'HARRY_POTTER') and ${r3_ece_qr_photo} != '' and (translate(normalize-space(${r4_lib_cipher_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'LIBRARY' or translate(normalize-space(${r4_lib_cipher_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CENTRAL LIBRARY') and translate(normalize-space(${r4_lib_start_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'TALL-NERD' and translate(normalize-space(${r4_lib_phy_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'LAST-LEG' and ${r4_lib_phy_photo} != ''</v>
-      </c>
-    </row>
-    <row r="61" xml:space="preserve">
-      <c r="A61" t="str">
+    <row r="63">
+      <c r="A63" t="str">
+        <v>select_one challenge_status_list</v>
+      </c>
+      <c r="B63" t="str">
+        <v>r4_challenge_status</v>
+      </c>
+      <c r="C63" t="str">
+        <v>Challenge Status (MANDATORY)</v>
+      </c>
+      <c r="D63" t="str">
+        <v>Select PASSED once completed with volunteer.</v>
+      </c>
+      <c r="E63" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F63" t="str">
+        <v>❌ Challenge status selection is mandatory.</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
         <v>note</v>
       </c>
-      <c r="B61" t="str">
-        <v>final_audi_stage_intro</v>
-      </c>
-      <c r="C61" t="str" xml:space="preserve">
-        <v xml:space="preserve">🏛️ FINAL CHALLENGES
-Proceed to the location and solve the two final riddles!
-Enter code in caps</v>
-      </c>
-      <c r="D61" t="str">
-        <v>Solve the final riddles.</v>
-      </c>
-    </row>
-    <row r="62" xml:space="preserve">
-      <c r="A62" t="str">
-        <v>text</v>
-      </c>
-      <c r="B62" t="str">
-        <v>final_riddle1_answer</v>
-      </c>
-      <c r="C62" t="str" xml:space="preserve">
-        <v xml:space="preserve">🧩 RIDDLE 1:
-"I am a place of darkness until the lights ignite. I hold hundreds of red seats, host grand orientations, and echo with voices through microphones. Where are you standing?"
-Enter code in caps</v>
-      </c>
-      <c r="D62" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
-      </c>
-      <c r="E62" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F62" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AUDITORIUM' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AUDI'</v>
-      </c>
-      <c r="G62" t="str">
-        <v>❌ Incorrect answer. Solve the riddle and enter in CAPS.</v>
-      </c>
-    </row>
-    <row r="63" xml:space="preserve">
-      <c r="A63" t="str">
-        <v>text</v>
-      </c>
-      <c r="B63" t="str">
-        <v>final_riddle2_stage_answer</v>
-      </c>
-      <c r="C63" t="str" xml:space="preserve">
-        <v xml:space="preserve">🎭 RIDDLE 2:
-"I am elevated above the crowd, where performers stand and spotlights shine. Underneath my wooden floor or behind the curtains, the ultimate secret waits. What am I?"
-Enter code in caps</v>
-      </c>
-      <c r="D63" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
-      </c>
-      <c r="E63" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F63" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'STAGE'</v>
-      </c>
-      <c r="G63" t="str">
-        <v>❌ Incorrect answer. Solve the stage riddle and enter in CAPS.</v>
-      </c>
-      <c r="H63" t="str">
-        <v>${team_name} != '' and ${team_id} != '' and ${team_start_photo} != '' and translate(normalize-space(${r1_mba_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ENG-KID-119' and ${r1_mba_photo} != '' and (translate(normalize-space(${r2_admin_block_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ADMIN' or translate(normalize-space(${r2_admin_block_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ADMIN BLOCK') and translate(normalize-space(${r2_admin_start_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ADMIN-START' and ((${r2_admin_variant} = 'var1' and translate(normalize-space(${r2_v1_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ADM-DUCK-3' and ${r2_v1_admin_photo} != '') or (${r2_admin_variant} = 'var2' and translate(normalize-space(${r2_v2_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ADM-DISNEY-3' and ${r2_v2_admin_photo} != '')) and (translate(normalize-space(${r3_ece_block_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ECE' or translate(normalize-space(${r3_ece_block_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ECE BLOCK') and translate(normalize-space(${r3_ece_start_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ECE-LETSGO' and (normalize-space(${r3_ece_qr_scan}) = 'HARRY_POTTER' or translate(normalize-space(${r3_ece_qr_scan}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'HARRY_POTTER') and ${r3_ece_qr_photo} != '' and (translate(normalize-space(${r4_lib_cipher_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'LIBRARY' or translate(normalize-space(${r4_lib_cipher_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CENTRAL LIBRARY') and translate(normalize-space(${r4_lib_start_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'TALL-NERD' and translate(normalize-space(${r4_lib_phy_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'LAST-LEG' and ${r4_lib_phy_photo} != '' and (translate(normalize-space(${final_riddle1_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AUDITORIUM' or translate(normalize-space(${final_riddle1_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AUDI')</v>
-      </c>
-    </row>
-    <row r="64" xml:space="preserve">
-      <c r="A64" t="str">
-        <v>image</v>
-      </c>
       <c r="B64" t="str">
-        <v>final_solved_puzzle_photo</v>
-      </c>
-      <c r="C64" t="str" xml:space="preserve">
-        <v xml:space="preserve">📸 Upload Photo of Your Solved Puzzle
-Photo upload is mandatory</v>
+        <v>r4_not_passed_note</v>
+      </c>
+      <c r="C64" t="str">
+        <v>⚠️ Please follow the organizer's instructions before continuing.</v>
       </c>
       <c r="D64" t="str">
-        <v>Take a clear photo of your team's completed/solved puzzle.</v>
-      </c>
-      <c r="E64" t="str">
-        <v>yes</v>
-      </c>
-      <c r="H64" t="str">
-        <v>${team_name} != '' and ${team_id} != '' and ${team_start_photo} != '' and translate(normalize-space(${r1_mba_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ENG-KID-119' and ${r1_mba_photo} != '' and (translate(normalize-space(${r2_admin_block_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ADMIN' or translate(normalize-space(${r2_admin_block_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ADMIN BLOCK') and translate(normalize-space(${r2_admin_start_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ADMIN-START' and ((${r2_admin_variant} = 'var1' and translate(normalize-space(${r2_v1_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ADM-DUCK-3' and ${r2_v1_admin_photo} != '') or (${r2_admin_variant} = 'var2' and translate(normalize-space(${r2_v2_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ADM-DISNEY-3' and ${r2_v2_admin_photo} != '')) and (translate(normalize-space(${r3_ece_block_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ECE' or translate(normalize-space(${r3_ece_block_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ECE BLOCK') and translate(normalize-space(${r3_ece_start_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ECE-LETSGO' and (normalize-space(${r3_ece_qr_scan}) = 'HARRY_POTTER' or translate(normalize-space(${r3_ece_qr_scan}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'HARRY_POTTER') and ${r3_ece_qr_photo} != '' and (translate(normalize-space(${r4_lib_cipher_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'LIBRARY' or translate(normalize-space(${r4_lib_cipher_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CENTRAL LIBRARY') and translate(normalize-space(${r4_lib_start_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'TALL-NERD' and translate(normalize-space(${r4_lib_phy_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'LAST-LEG' and ${r4_lib_phy_photo} != '' and (translate(normalize-space(${final_riddle1_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AUDITORIUM' or translate(normalize-space(${final_riddle1_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AUDI') and translate(normalize-space(${final_riddle2_stage_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'STAGE'</v>
+        <v>Complete the physical challenge as instructed.</v>
+      </c>
+      <c r="I64" t="str">
+        <v>${r4_challenge_status} = 'not_passed'</v>
       </c>
     </row>
     <row r="65" xml:space="preserve">
       <c r="A65" t="str">
-        <v>text</v>
+        <v>image</v>
       </c>
       <c r="B65" t="str">
-        <v>final_stage_volunteer_code</v>
+        <v>r4_lib_phy_photo</v>
       </c>
       <c r="C65" t="str" xml:space="preserve">
-        <v xml:space="preserve">Enter Final Volunteer Clearance Code
-Enter code in caps</v>
+        <v xml:space="preserve">📸 Upload Photo of Physical Challenge Completion (MANDATORY)
+Photo upload is mandatory</v>
       </c>
       <c r="D65" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>Take a clear photo of your team completing the physical challenge.</v>
       </c>
       <c r="E65" t="str">
         <v>yes</v>
       </c>
       <c r="F65" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'FINAL-PATH3' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'FINAL-PATH1' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'FINAL-PATH2'</v>
-      </c>
-      <c r="G65" t="str">
-        <v>❌ Incorrect code. Enter the code in CAPS provided by the Chief Judge.</v>
-      </c>
-      <c r="H65" t="str">
-        <v>${team_name} != '' and ${team_id} != '' and ${team_start_photo} != '' and translate(normalize-space(${r1_mba_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ENG-KID-119' and ${r1_mba_photo} != '' and (translate(normalize-space(${r2_admin_block_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ADMIN' or translate(normalize-space(${r2_admin_block_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ADMIN BLOCK') and translate(normalize-space(${r2_admin_start_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ADMIN-START' and ((${r2_admin_variant} = 'var1' and translate(normalize-space(${r2_v1_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ADM-DUCK-3' and ${r2_v1_admin_photo} != '') or (${r2_admin_variant} = 'var2' and translate(normalize-space(${r2_v2_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ADM-DISNEY-3' and ${r2_v2_admin_photo} != '')) and (translate(normalize-space(${r3_ece_block_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ECE' or translate(normalize-space(${r3_ece_block_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ECE BLOCK') and translate(normalize-space(${r3_ece_start_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ECE-LETSGO' and (normalize-space(${r3_ece_qr_scan}) = 'HARRY_POTTER' or translate(normalize-space(${r3_ece_qr_scan}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'HARRY_POTTER') and ${r3_ece_qr_photo} != '' and (translate(normalize-space(${r4_lib_cipher_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'LIBRARY' or translate(normalize-space(${r4_lib_cipher_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CENTRAL LIBRARY') and translate(normalize-space(${r4_lib_start_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'TALL-NERD' and translate(normalize-space(${r4_lib_phy_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'LAST-LEG' and ${r4_lib_phy_photo} != '' and (translate(normalize-space(${final_riddle1_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AUDITORIUM' or translate(normalize-space(${final_riddle1_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AUDI') and translate(normalize-space(${final_riddle2_stage_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'STAGE'</v>
+        <v>❌ Challenge photo upload is mandatory.</v>
+      </c>
+      <c r="I65" t="str">
+        <v>${r4_challenge_status} = 'passed'</v>
       </c>
     </row>
     <row r="66" xml:space="preserve">
       <c r="A66" t="str">
-        <v>note</v>
+        <v>text</v>
       </c>
       <c r="B66" t="str">
-        <v>final_congratulations_screen</v>
+        <v>r4_lib_phy_code</v>
       </c>
       <c r="C66" t="str" xml:space="preserve">
-        <v xml:space="preserve">🎉 CONGRATULATIONS! PATH 3 COMPLETED.
-🏆 You have successfully conquered every challenge, puzzle, and cipher on PATH 3!
-Show this completion screen immediately to the Chief Judge to lock in your finishing timestamp and rank!</v>
+        <v xml:space="preserve">Enter Volunteer Completion Code (MANDATORY)
+Enter code in caps</v>
       </c>
       <c r="D66" t="str">
-        <v>Report to Chief Judge to finalize completion.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+      </c>
+      <c r="E66" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F66" t="str">
+        <v>❌ Volunteer completion code is mandatory.</v>
+      </c>
+      <c r="G66" t="str">
+        <v>regex(., '^[A-Z0-9\-_]+$') and normalize-space(.) = 'LAST-LEG'</v>
       </c>
       <c r="H66" t="str">
-        <v>${team_name} != '' and ${team_id} != '' and ${team_start_photo} != '' and translate(normalize-space(${r1_mba_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ENG-KID-119' and ${r1_mba_photo} != '' and (translate(normalize-space(${r2_admin_block_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ADMIN' or translate(normalize-space(${r2_admin_block_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ADMIN BLOCK') and translate(normalize-space(${r2_admin_start_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ADMIN-START' and ((${r2_admin_variant} = 'var1' and translate(normalize-space(${r2_v1_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ADM-DUCK-3' and ${r2_v1_admin_photo} != '') or (${r2_admin_variant} = 'var2' and translate(normalize-space(${r2_v2_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ADM-DISNEY-3' and ${r2_v2_admin_photo} != '')) and (translate(normalize-space(${r3_ece_block_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ECE' or translate(normalize-space(${r3_ece_block_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ECE BLOCK') and translate(normalize-space(${r3_ece_start_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ECE-LETSGO' and (normalize-space(${r3_ece_qr_scan}) = 'HARRY_POTTER' or translate(normalize-space(${r3_ece_qr_scan}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'HARRY_POTTER') and ${r3_ece_qr_photo} != '' and (translate(normalize-space(${r4_lib_cipher_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'LIBRARY' or translate(normalize-space(${r4_lib_cipher_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CENTRAL LIBRARY') and translate(normalize-space(${r4_lib_start_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'TALL-NERD' and translate(normalize-space(${r4_lib_phy_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'LAST-LEG' and ${r4_lib_phy_photo} != '' and (translate(normalize-space(${final_riddle1_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AUDITORIUM' or translate(normalize-space(${final_riddle1_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AUDI') and translate(normalize-space(${final_riddle2_stage_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'STAGE' and (translate(normalize-space(${final_stage_volunteer_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'FINAL-PATH3' or translate(normalize-space(${final_stage_volunteer_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'FINAL-PATH1' or translate(normalize-space(${final_stage_volunteer_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'FINAL-PATH2') and ${final_solved_puzzle_photo} != ''</v>
+        <v>❌ Incorrect code. Enter LAST-LEG in CAPS provided by the volunteer.</v>
+      </c>
+      <c r="I66" t="str">
+        <v>${r4_challenge_status} = 'passed'</v>
       </c>
     </row>
     <row r="67">
@@ -1495,16 +1737,209 @@
         <v>end_group</v>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>begin_group</v>
+      </c>
+      <c r="B68" t="str">
+        <v>final_puzzles_group</v>
+      </c>
+      <c r="C68" t="str">
+        <v>FINAL ROUND</v>
+      </c>
+      <c r="I68" t="str">
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_mba_code}) = 'ENG-KID-119' and ${r1_mba_photo} != '' and (normalize-space(${r2_admin_block_answer}) = 'ADMIN' or normalize-space(${r2_admin_block_answer}) = 'ADMIN BLOCK') and normalize-space(${r2_admin_start_code}) = 'ADMIN-START' and ((${r2_admin_variant} = 'var1' and normalize-space(${r2_v1_code}) = 'ADM-DUCK-3' and ${r2_v1_admin_photo} != '') or (${r2_admin_variant} = 'var2' and normalize-space(${r2_v2_code}) = 'ADM-DISNEY-3' and ${r2_v2_admin_photo} != '')) and (normalize-space(${r3_ece_block_answer}) = 'ECE' or normalize-space(${r3_ece_block_answer}) = 'ECE BLOCK') and normalize-space(${r3_ece_qr_scan}) = 'HARRY_POTTER' and ${r3_ece_qr_photo} != '' and (normalize-space(${r4_lib_cipher_answer}) = 'LIBRARY' or normalize-space(${r4_lib_cipher_answer}) = 'CENTRAL LIBRARY') and normalize-space(${r4_lib_start_code}) = 'TALL-NERD' and ${r4_challenge_status} = 'passed' and normalize-space(${r4_lib_phy_code}) = 'LAST-LEG' and ${r4_lib_phy_photo} != ''</v>
+      </c>
+    </row>
+    <row r="69" xml:space="preserve">
+      <c r="A69" t="str">
+        <v>note</v>
+      </c>
+      <c r="B69" t="str">
+        <v>final_audi_stage_intro</v>
+      </c>
+      <c r="C69" t="str" xml:space="preserve">
+        <v xml:space="preserve">🏛️ FINAL ROUND — RIDDLES
+Solve the two final riddles to reveal the final destination!
+Enter code in caps</v>
+      </c>
+      <c r="D69" t="str">
+        <v>Solve the final riddles in CAPS.</v>
+      </c>
+    </row>
+    <row r="70" xml:space="preserve">
+      <c r="A70" t="str">
+        <v>text</v>
+      </c>
+      <c r="B70" t="str">
+        <v>final_riddle1_answer</v>
+      </c>
+      <c r="C70" t="str" xml:space="preserve">
+        <v xml:space="preserve">🧩 AUDITORIUM RIDDLE: (MANDATORY)
+"I am empty, yet I am built for crowds.
+I have a stage, but no actors of my own.
+I have countless seats, but none are meant to sleep.
+When a voice rises before me, silence falls behind me.
+When the lights awaken, all eyes face one direction.
+What am I?"
+Enter code in caps</v>
+      </c>
+      <c r="D70" t="str">
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+      </c>
+      <c r="E70" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F70" t="str">
+        <v>❌ Solving Riddle 1 is mandatory.</v>
+      </c>
+      <c r="G70" t="str">
+        <v>regex(., '^[A-Z ]+$') and (normalize-space(.) = 'AUDITORIUM' or normalize-space(.) = 'AUDI')</v>
+      </c>
+      <c r="H70" t="str">
+        <v>❌ Incorrect answer. Solve Riddle 1 and enter in UPPERCASE (CAPS ONLY).</v>
+      </c>
+    </row>
+    <row r="71" xml:space="preserve">
+      <c r="A71" t="str">
+        <v>text</v>
+      </c>
+      <c r="B71" t="str">
+        <v>final_riddle2_stage_answer</v>
+      </c>
+      <c r="C71" t="str" xml:space="preserve">
+        <v xml:space="preserve">🎭 STAGE RIDDLE: (MANDATORY)
+"I am elevated above the crowd, where performers stand and spotlights shine.
+Underneath my wooden floor or behind the curtains, the ultimate secret waits.
+What am I?"
+Enter code in caps</v>
+      </c>
+      <c r="D71" t="str">
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+      </c>
+      <c r="E71" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F71" t="str">
+        <v>❌ Solving Riddle 2 is mandatory.</v>
+      </c>
+      <c r="G71" t="str">
+        <v>regex(., '^[A-Z ]+$') and normalize-space(.) = 'STAGE'</v>
+      </c>
+      <c r="H71" t="str">
+        <v>❌ Incorrect answer. Solve Riddle 2 and enter in UPPERCASE (CAPS ONLY).</v>
+      </c>
+      <c r="I71" t="str">
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_mba_code}) = 'ENG-KID-119' and ${r1_mba_photo} != '' and (normalize-space(${r2_admin_block_answer}) = 'ADMIN' or normalize-space(${r2_admin_block_answer}) = 'ADMIN BLOCK') and normalize-space(${r2_admin_start_code}) = 'ADMIN-START' and ((${r2_admin_variant} = 'var1' and normalize-space(${r2_v1_code}) = 'ADM-DUCK-3' and ${r2_v1_admin_photo} != '') or (${r2_admin_variant} = 'var2' and normalize-space(${r2_v2_code}) = 'ADM-DISNEY-3' and ${r2_v2_admin_photo} != '')) and (normalize-space(${r3_ece_block_answer}) = 'ECE' or normalize-space(${r3_ece_block_answer}) = 'ECE BLOCK') and normalize-space(${r3_ece_qr_scan}) = 'HARRY_POTTER' and ${r3_ece_qr_photo} != '' and (normalize-space(${r4_lib_cipher_answer}) = 'LIBRARY' or normalize-space(${r4_lib_cipher_answer}) = 'CENTRAL LIBRARY') and normalize-space(${r4_lib_start_code}) = 'TALL-NERD' and ${r4_challenge_status} = 'passed' and normalize-space(${r4_lib_phy_code}) = 'LAST-LEG' and ${r4_lib_phy_photo} != '' and (normalize-space(${final_riddle1_answer}) = 'AUDITORIUM' or normalize-space(${final_riddle1_answer}) = 'AUDI')</v>
+      </c>
+    </row>
+    <row r="72" xml:space="preserve">
+      <c r="A72" t="str">
+        <v>note</v>
+      </c>
+      <c r="B72" t="str">
+        <v>final_proceed_stage_note</v>
+      </c>
+      <c r="C72" t="str" xml:space="preserve">
+        <v xml:space="preserve">🏃 Proceed to the final location identified!
+Solve the final puzzle at the stage, upload a photo of the completed puzzle, and get your clearance code from the Chief Judge!
+Enter code in caps</v>
+      </c>
+      <c r="D72" t="str">
+        <v>Go to the stage to solve the final puzzle.</v>
+      </c>
+      <c r="I72" t="str">
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_mba_code}) = 'ENG-KID-119' and ${r1_mba_photo} != '' and (normalize-space(${r2_admin_block_answer}) = 'ADMIN' or normalize-space(${r2_admin_block_answer}) = 'ADMIN BLOCK') and normalize-space(${r2_admin_start_code}) = 'ADMIN-START' and ((${r2_admin_variant} = 'var1' and normalize-space(${r2_v1_code}) = 'ADM-DUCK-3' and ${r2_v1_admin_photo} != '') or (${r2_admin_variant} = 'var2' and normalize-space(${r2_v2_code}) = 'ADM-DISNEY-3' and ${r2_v2_admin_photo} != '')) and (normalize-space(${r3_ece_block_answer}) = 'ECE' or normalize-space(${r3_ece_block_answer}) = 'ECE BLOCK') and normalize-space(${r3_ece_qr_scan}) = 'HARRY_POTTER' and ${r3_ece_qr_photo} != '' and (normalize-space(${r4_lib_cipher_answer}) = 'LIBRARY' or normalize-space(${r4_lib_cipher_answer}) = 'CENTRAL LIBRARY') and normalize-space(${r4_lib_start_code}) = 'TALL-NERD' and ${r4_challenge_status} = 'passed' and normalize-space(${r4_lib_phy_code}) = 'LAST-LEG' and ${r4_lib_phy_photo} != '' and (normalize-space(${final_riddle1_answer}) = 'AUDITORIUM' or normalize-space(${final_riddle1_answer}) = 'AUDI') and normalize-space(${final_riddle2_stage_answer}) = 'STAGE'</v>
+      </c>
+    </row>
+    <row r="73" xml:space="preserve">
+      <c r="A73" t="str">
+        <v>image</v>
+      </c>
+      <c r="B73" t="str">
+        <v>final_solved_puzzle_photo</v>
+      </c>
+      <c r="C73" t="str" xml:space="preserve">
+        <v xml:space="preserve">📸 Upload Photo of Your Solved Puzzle (MANDATORY)
+Photo upload is mandatory</v>
+      </c>
+      <c r="D73" t="str">
+        <v>Take a clear photo of your team's completed/solved puzzle.</v>
+      </c>
+      <c r="E73" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F73" t="str">
+        <v>❌ Photo of the solved puzzle is mandatory.</v>
+      </c>
+      <c r="I73" t="str">
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_mba_code}) = 'ENG-KID-119' and ${r1_mba_photo} != '' and (normalize-space(${r2_admin_block_answer}) = 'ADMIN' or normalize-space(${r2_admin_block_answer}) = 'ADMIN BLOCK') and normalize-space(${r2_admin_start_code}) = 'ADMIN-START' and ((${r2_admin_variant} = 'var1' and normalize-space(${r2_v1_code}) = 'ADM-DUCK-3' and ${r2_v1_admin_photo} != '') or (${r2_admin_variant} = 'var2' and normalize-space(${r2_v2_code}) = 'ADM-DISNEY-3' and ${r2_v2_admin_photo} != '')) and (normalize-space(${r3_ece_block_answer}) = 'ECE' or normalize-space(${r3_ece_block_answer}) = 'ECE BLOCK') and normalize-space(${r3_ece_qr_scan}) = 'HARRY_POTTER' and ${r3_ece_qr_photo} != '' and (normalize-space(${r4_lib_cipher_answer}) = 'LIBRARY' or normalize-space(${r4_lib_cipher_answer}) = 'CENTRAL LIBRARY') and normalize-space(${r4_lib_start_code}) = 'TALL-NERD' and ${r4_challenge_status} = 'passed' and normalize-space(${r4_lib_phy_code}) = 'LAST-LEG' and ${r4_lib_phy_photo} != '' and (normalize-space(${final_riddle1_answer}) = 'AUDITORIUM' or normalize-space(${final_riddle1_answer}) = 'AUDI') and normalize-space(${final_riddle2_stage_answer}) = 'STAGE'</v>
+      </c>
+    </row>
+    <row r="74" xml:space="preserve">
+      <c r="A74" t="str">
+        <v>text</v>
+      </c>
+      <c r="B74" t="str">
+        <v>final_stage_volunteer_code</v>
+      </c>
+      <c r="C74" t="str" xml:space="preserve">
+        <v xml:space="preserve">Enter Final Volunteer Clearance Code (MANDATORY)
+Enter code in caps</v>
+      </c>
+      <c r="D74" t="str">
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+      </c>
+      <c r="E74" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F74" t="str">
+        <v>❌ Final clearance code is mandatory.</v>
+      </c>
+      <c r="G74" t="str">
+        <v>regex(., '^[A-Z0-9\-_]+$') and (normalize-space(.) = 'FINAL-PATH3' or normalize-space(.) = 'FINAL-PATH1' or normalize-space(.) = 'FINAL-PATH2')</v>
+      </c>
+      <c r="H74" t="str">
+        <v>❌ Incorrect code. Enter the code in UPPERCASE (CAPS ONLY) provided by the Chief Judge.</v>
+      </c>
+      <c r="I74" t="str">
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_mba_code}) = 'ENG-KID-119' and ${r1_mba_photo} != '' and (normalize-space(${r2_admin_block_answer}) = 'ADMIN' or normalize-space(${r2_admin_block_answer}) = 'ADMIN BLOCK') and normalize-space(${r2_admin_start_code}) = 'ADMIN-START' and ((${r2_admin_variant} = 'var1' and normalize-space(${r2_v1_code}) = 'ADM-DUCK-3' and ${r2_v1_admin_photo} != '') or (${r2_admin_variant} = 'var2' and normalize-space(${r2_v2_code}) = 'ADM-DISNEY-3' and ${r2_v2_admin_photo} != '')) and (normalize-space(${r3_ece_block_answer}) = 'ECE' or normalize-space(${r3_ece_block_answer}) = 'ECE BLOCK') and normalize-space(${r3_ece_qr_scan}) = 'HARRY_POTTER' and ${r3_ece_qr_photo} != '' and (normalize-space(${r4_lib_cipher_answer}) = 'LIBRARY' or normalize-space(${r4_lib_cipher_answer}) = 'CENTRAL LIBRARY') and normalize-space(${r4_lib_start_code}) = 'TALL-NERD' and ${r4_challenge_status} = 'passed' and normalize-space(${r4_lib_phy_code}) = 'LAST-LEG' and ${r4_lib_phy_photo} != '' and (normalize-space(${final_riddle1_answer}) = 'AUDITORIUM' or normalize-space(${final_riddle1_answer}) = 'AUDI') and normalize-space(${final_riddle2_stage_answer}) = 'STAGE'</v>
+      </c>
+    </row>
+    <row r="75" xml:space="preserve">
+      <c r="A75" t="str">
+        <v>note</v>
+      </c>
+      <c r="B75" t="str">
+        <v>final_congratulations_screen</v>
+      </c>
+      <c r="C75" t="str" xml:space="preserve">
+        <v xml:space="preserve">🎉 CONGRATULATIONS! YOU HAVE COMPLETED PATH 3!
+🏆 You have successfully entered the final clearance code!
+🔔 NOW RUN TO GO RING THE BELL TO WIN THE GAME! 🔔🏃💨</v>
+      </c>
+      <c r="D75" t="str">
+        <v>Run to ring the bell to claim victory!</v>
+      </c>
+      <c r="I75" t="str">
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_mba_code}) = 'ENG-KID-119' and ${r1_mba_photo} != '' and (normalize-space(${r2_admin_block_answer}) = 'ADMIN' or normalize-space(${r2_admin_block_answer}) = 'ADMIN BLOCK') and normalize-space(${r2_admin_start_code}) = 'ADMIN-START' and ((${r2_admin_variant} = 'var1' and normalize-space(${r2_v1_code}) = 'ADM-DUCK-3' and ${r2_v1_admin_photo} != '') or (${r2_admin_variant} = 'var2' and normalize-space(${r2_v2_code}) = 'ADM-DISNEY-3' and ${r2_v2_admin_photo} != '')) and (normalize-space(${r3_ece_block_answer}) = 'ECE' or normalize-space(${r3_ece_block_answer}) = 'ECE BLOCK') and normalize-space(${r3_ece_qr_scan}) = 'HARRY_POTTER' and ${r3_ece_qr_photo} != '' and (normalize-space(${r4_lib_cipher_answer}) = 'LIBRARY' or normalize-space(${r4_lib_cipher_answer}) = 'CENTRAL LIBRARY') and normalize-space(${r4_lib_start_code}) = 'TALL-NERD' and ${r4_challenge_status} = 'passed' and normalize-space(${r4_lib_phy_code}) = 'LAST-LEG' and ${r4_lib_phy_photo} != '' and (normalize-space(${final_riddle1_answer}) = 'AUDITORIUM' or normalize-space(${final_riddle1_answer}) = 'AUDI') and normalize-space(${final_riddle2_stage_answer}) = 'STAGE' and (normalize-space(${final_stage_volunteer_code}) = 'FINAL-PATH3' or normalize-space(${final_stage_volunteer_code}) = 'FINAL-PATH1' or normalize-space(${final_stage_volunteer_code}) = 'FINAL-PATH2') and ${final_solved_puzzle_photo} != ''</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>end_group</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I67"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J76"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1525,7 +1960,7 @@
         <v>var1</v>
       </c>
       <c r="C2" t="str">
-        <v>Variant 1: ADM-02 — Count to Unlock</v>
+        <v>Variant A: Count to Unlock</v>
       </c>
     </row>
     <row r="3">
@@ -1536,12 +1971,78 @@
         <v>var2</v>
       </c>
       <c r="C3" t="str">
-        <v>Variant 2: ADM-02 — Memory Room</v>
+        <v>Variant B: Memory Room</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>clock_time_choices</v>
+      </c>
+      <c r="B4" t="str">
+        <v>t_1015</v>
+      </c>
+      <c r="C4" t="str">
+        <v>10:15</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>clock_time_choices</v>
+      </c>
+      <c r="B5" t="str">
+        <v>t_1200</v>
+      </c>
+      <c r="C5" t="str">
+        <v>12:00</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>clock_time_choices</v>
+      </c>
+      <c r="B6" t="str">
+        <v>t_0230</v>
+      </c>
+      <c r="C6" t="str">
+        <v>02:30</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>clock_time_choices</v>
+      </c>
+      <c r="B7" t="str">
+        <v>t_0445</v>
+      </c>
+      <c r="C7" t="str">
+        <v>04:45</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>challenge_status_list</v>
+      </c>
+      <c r="B8" t="str">
+        <v>passed</v>
+      </c>
+      <c r="C8" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>challenge_status_list</v>
+      </c>
+      <c r="B9" t="str">
+        <v>not_passed</v>
+      </c>
+      <c r="C9" t="str">
+        <v>NOT PASSED</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C9"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1569,10 +2070,10 @@
         <v>FINAL CLUE — PATH 3</v>
       </c>
       <c r="B2" t="str">
-        <v>final_clue_path3</v>
+        <v>PATH3_TREASURE_HUNT</v>
       </c>
       <c r="C2" t="str">
-        <v>20260902</v>
+        <v>20260904</v>
       </c>
       <c r="D2" t="str">
         <v>default</v>

--- a/ROUTE_3_PATH3_MBA_ADMIN_ECE_LIB_AUDI/PATH3_FINAL_ODK.xlsx
+++ b/ROUTE_3_PATH3_MBA_ADMIN_ECE_LIB_AUDI/PATH3_FINAL_ODK.xlsx
@@ -483,7 +483,8 @@
 * Next 15 teams proceed to Round 3.
 * Next 7 teams proceed to Round 4.
 * Next 2 teams proceed to Round 5.
-⚠️ MANDATORY RESPONSE &amp; CAPS ONLY RULES:
+⚠️ STRICT PROGRESSION &amp; MANDATORY RULES:
+• Read each question properly as you cannot come back to the question once you go ahead!
 • Every single question, photo upload, and code entry is strictly MANDATORY.
 • All text answers and volunteer codes must be entered in UPPERCASE (CAPS ONLY).
 • Lowercase letters will be rejected by validation.</v>
@@ -504,7 +505,7 @@
 Enter code in caps</v>
       </c>
       <c r="D4" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E4" t="str">
         <v>yes</v>
@@ -531,7 +532,7 @@
 Enter code in caps</v>
       </c>
       <c r="D5" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E5" t="str">
         <v>yes</v>
@@ -639,7 +640,7 @@
 Enter code in caps</v>
       </c>
       <c r="D11" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E11" t="str">
         <v>yes</v>
@@ -705,7 +706,7 @@
 Enter code in caps</v>
       </c>
       <c r="D15" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E15" t="str">
         <v>yes</v>
@@ -753,7 +754,7 @@
 Enter code in caps</v>
       </c>
       <c r="D17" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E17" t="str">
         <v>yes</v>
@@ -1007,7 +1008,7 @@
 Enter code in caps</v>
       </c>
       <c r="D29" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E29" t="str">
         <v>yes</v>
@@ -1072,7 +1073,7 @@
 Enter code in caps</v>
       </c>
       <c r="D33" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E33" t="str">
         <v>yes</v>
@@ -1125,7 +1126,7 @@
 Enter code in caps</v>
       </c>
       <c r="D35" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E35" t="str">
         <v>yes</v>
@@ -1152,7 +1153,7 @@
 Enter code in caps</v>
       </c>
       <c r="D36" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E36" t="str">
         <v>yes</v>
@@ -1179,7 +1180,7 @@
 Enter code in caps</v>
       </c>
       <c r="D37" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E37" t="str">
         <v>yes</v>
@@ -1206,7 +1207,7 @@
 Enter code in caps</v>
       </c>
       <c r="D38" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E38" t="str">
         <v>yes</v>
@@ -1233,7 +1234,7 @@
 Enter code in caps</v>
       </c>
       <c r="D39" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E39" t="str">
         <v>yes</v>
@@ -1302,7 +1303,7 @@
 Enter code in caps</v>
       </c>
       <c r="D42" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E42" t="str">
         <v>yes</v>
@@ -1375,7 +1376,7 @@
 Enter code in caps</v>
       </c>
       <c r="D47" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E47" t="str">
         <v>yes</v>
@@ -1455,7 +1456,7 @@
         <v>Scan Discovered QR Code (MANDATORY)</v>
       </c>
       <c r="D52" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E52" t="str">
         <v>yes</v>
@@ -1543,7 +1544,7 @@
 Enter code in caps</v>
       </c>
       <c r="D57" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E57" t="str">
         <v>yes</v>
@@ -1588,7 +1589,7 @@
 Enter code in caps</v>
       </c>
       <c r="D59" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E59" t="str">
         <v>yes</v>
@@ -1714,7 +1715,7 @@
 Enter code in caps</v>
       </c>
       <c r="D66" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E66" t="str">
         <v>yes</v>
@@ -1785,7 +1786,7 @@
 Enter code in caps</v>
       </c>
       <c r="D70" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E70" t="str">
         <v>yes</v>
@@ -1815,7 +1816,7 @@
 Enter code in caps</v>
       </c>
       <c r="D71" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E71" t="str">
         <v>yes</v>
@@ -1888,7 +1889,7 @@
 Enter code in caps</v>
       </c>
       <c r="D74" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E74" t="str">
         <v>yes</v>
